--- a/Project 1 Data Quality Assessment/D2 Temporal Continuity & Information Availability/artifacts/data/D2_process_floor_casebook.xlsx
+++ b/Project 1 Data Quality Assessment/D2 Temporal Continuity & Information Availability/artifacts/data/D2_process_floor_casebook.xlsx
@@ -710,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L285"/>
+  <dimension ref="A1:N285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -756,20 +756,30 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>soft_rle_diagnostic</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>soft_stasis</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>floor_occupancy</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>resolution_limited</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>sensor_freeze</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>qfa_unavailable</t>
         </is>
@@ -803,15 +813,21 @@
         <v>0</v>
       </c>
       <c r="I2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
       </c>
       <c r="K2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -843,15 +859,21 @@
         <v>0</v>
       </c>
       <c r="I3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
       </c>
       <c r="K3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M3" t="b">
+        <v>0</v>
+      </c>
+      <c r="N3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -883,15 +905,21 @@
         <v>0</v>
       </c>
       <c r="I4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
       </c>
       <c r="K4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="b">
+        <v>0</v>
+      </c>
+      <c r="M4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -923,15 +951,21 @@
         <v>0</v>
       </c>
       <c r="I5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
       </c>
       <c r="K5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M5" t="b">
+        <v>0</v>
+      </c>
+      <c r="N5" t="b">
         <v>0</v>
       </c>
     </row>
@@ -963,15 +997,21 @@
         <v>0</v>
       </c>
       <c r="I6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
       </c>
       <c r="K6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="b">
+        <v>0</v>
+      </c>
+      <c r="M6" t="b">
+        <v>0</v>
+      </c>
+      <c r="N6" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1003,15 +1043,21 @@
         <v>0</v>
       </c>
       <c r="I7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
       </c>
       <c r="K7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="b">
+        <v>0</v>
+      </c>
+      <c r="M7" t="b">
+        <v>0</v>
+      </c>
+      <c r="N7" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1043,15 +1089,21 @@
         <v>0</v>
       </c>
       <c r="I8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
       </c>
       <c r="K8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="b">
+        <v>0</v>
+      </c>
+      <c r="M8" t="b">
+        <v>0</v>
+      </c>
+      <c r="N8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1083,15 +1135,21 @@
         <v>0</v>
       </c>
       <c r="I9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
       </c>
       <c r="K9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="b">
+        <v>0</v>
+      </c>
+      <c r="M9" t="b">
+        <v>0</v>
+      </c>
+      <c r="N9" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1123,15 +1181,21 @@
         <v>0</v>
       </c>
       <c r="I10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
       </c>
       <c r="K10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="b">
+        <v>0</v>
+      </c>
+      <c r="M10" t="b">
+        <v>0</v>
+      </c>
+      <c r="N10" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1163,15 +1227,21 @@
         <v>0</v>
       </c>
       <c r="I11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
       </c>
       <c r="K11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="b">
+        <v>0</v>
+      </c>
+      <c r="M11" t="b">
+        <v>0</v>
+      </c>
+      <c r="N11" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1203,15 +1273,21 @@
         <v>0</v>
       </c>
       <c r="I12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
       </c>
       <c r="K12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="b">
+        <v>0</v>
+      </c>
+      <c r="M12" t="b">
+        <v>0</v>
+      </c>
+      <c r="N12" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1243,15 +1319,21 @@
         <v>0</v>
       </c>
       <c r="I13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
       </c>
       <c r="K13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="b">
+        <v>0</v>
+      </c>
+      <c r="M13" t="b">
+        <v>0</v>
+      </c>
+      <c r="N13" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1283,15 +1365,21 @@
         <v>0</v>
       </c>
       <c r="I14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
       </c>
       <c r="K14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="b">
+        <v>0</v>
+      </c>
+      <c r="M14" t="b">
+        <v>0</v>
+      </c>
+      <c r="N14" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1323,15 +1411,21 @@
         <v>0</v>
       </c>
       <c r="I15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
       </c>
       <c r="K15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="b">
+        <v>0</v>
+      </c>
+      <c r="M15" t="b">
+        <v>0</v>
+      </c>
+      <c r="N15" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1363,15 +1457,21 @@
         <v>1</v>
       </c>
       <c r="I16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="b">
         <v>1</v>
       </c>
       <c r="K16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="b">
+        <v>1</v>
+      </c>
+      <c r="M16" t="b">
+        <v>0</v>
+      </c>
+      <c r="N16" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1403,15 +1503,21 @@
         <v>1</v>
       </c>
       <c r="I17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" t="b">
         <v>1</v>
       </c>
       <c r="K17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M17" t="b">
+        <v>0</v>
+      </c>
+      <c r="N17" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1443,15 +1549,21 @@
         <v>1</v>
       </c>
       <c r="I18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" t="b">
         <v>1</v>
       </c>
       <c r="K18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M18" t="b">
+        <v>0</v>
+      </c>
+      <c r="N18" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1483,15 +1595,21 @@
         <v>1</v>
       </c>
       <c r="I19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="b">
         <v>1</v>
       </c>
       <c r="K19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="b">
+        <v>1</v>
+      </c>
+      <c r="M19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N19" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1523,15 +1641,21 @@
         <v>1</v>
       </c>
       <c r="I20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" t="b">
         <v>1</v>
       </c>
       <c r="K20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="b">
+        <v>1</v>
+      </c>
+      <c r="M20" t="b">
+        <v>0</v>
+      </c>
+      <c r="N20" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1563,15 +1687,21 @@
         <v>1</v>
       </c>
       <c r="I21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" t="b">
         <v>1</v>
       </c>
       <c r="K21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="b">
+        <v>1</v>
+      </c>
+      <c r="M21" t="b">
+        <v>0</v>
+      </c>
+      <c r="N21" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1603,15 +1733,21 @@
         <v>1</v>
       </c>
       <c r="I22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" t="b">
         <v>1</v>
       </c>
       <c r="K22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" t="b">
+        <v>1</v>
+      </c>
+      <c r="M22" t="b">
+        <v>0</v>
+      </c>
+      <c r="N22" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1643,15 +1779,21 @@
         <v>1</v>
       </c>
       <c r="I23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" t="b">
         <v>1</v>
       </c>
       <c r="K23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="b">
+        <v>1</v>
+      </c>
+      <c r="M23" t="b">
+        <v>0</v>
+      </c>
+      <c r="N23" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1683,15 +1825,21 @@
         <v>1</v>
       </c>
       <c r="I24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" t="b">
         <v>1</v>
       </c>
       <c r="K24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" t="b">
+        <v>1</v>
+      </c>
+      <c r="M24" t="b">
+        <v>0</v>
+      </c>
+      <c r="N24" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1723,15 +1871,21 @@
         <v>1</v>
       </c>
       <c r="I25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" t="b">
         <v>1</v>
       </c>
       <c r="K25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" t="b">
+        <v>1</v>
+      </c>
+      <c r="M25" t="b">
+        <v>0</v>
+      </c>
+      <c r="N25" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1763,15 +1917,21 @@
         <v>1</v>
       </c>
       <c r="I26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="b">
         <v>1</v>
       </c>
       <c r="K26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="b">
+        <v>1</v>
+      </c>
+      <c r="M26" t="b">
+        <v>0</v>
+      </c>
+      <c r="N26" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1803,15 +1963,21 @@
         <v>1</v>
       </c>
       <c r="I27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" t="b">
         <v>1</v>
       </c>
       <c r="K27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="b">
+        <v>1</v>
+      </c>
+      <c r="M27" t="b">
+        <v>0</v>
+      </c>
+      <c r="N27" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1843,15 +2009,21 @@
         <v>1</v>
       </c>
       <c r="I28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" t="b">
         <v>1</v>
       </c>
       <c r="K28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" t="b">
+        <v>1</v>
+      </c>
+      <c r="M28" t="b">
+        <v>0</v>
+      </c>
+      <c r="N28" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1883,15 +2055,21 @@
         <v>1</v>
       </c>
       <c r="I29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" t="b">
         <v>1</v>
       </c>
       <c r="K29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M29" t="b">
+        <v>0</v>
+      </c>
+      <c r="N29" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1923,15 +2101,21 @@
         <v>1</v>
       </c>
       <c r="I30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J30" t="b">
         <v>1</v>
       </c>
       <c r="K30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" t="b">
+        <v>1</v>
+      </c>
+      <c r="M30" t="b">
+        <v>0</v>
+      </c>
+      <c r="N30" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1963,15 +2147,21 @@
         <v>1</v>
       </c>
       <c r="I31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" t="b">
         <v>1</v>
       </c>
       <c r="K31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" t="b">
+        <v>1</v>
+      </c>
+      <c r="M31" t="b">
+        <v>0</v>
+      </c>
+      <c r="N31" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2003,15 +2193,21 @@
         <v>1</v>
       </c>
       <c r="I32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" t="b">
         <v>1</v>
       </c>
       <c r="K32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" t="b">
+        <v>1</v>
+      </c>
+      <c r="M32" t="b">
+        <v>0</v>
+      </c>
+      <c r="N32" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2043,15 +2239,21 @@
         <v>1</v>
       </c>
       <c r="I33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" t="b">
         <v>1</v>
       </c>
       <c r="K33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" t="b">
+        <v>1</v>
+      </c>
+      <c r="M33" t="b">
+        <v>0</v>
+      </c>
+      <c r="N33" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2083,15 +2285,21 @@
         <v>1</v>
       </c>
       <c r="I34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" t="b">
         <v>1</v>
       </c>
       <c r="K34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" t="b">
+        <v>1</v>
+      </c>
+      <c r="M34" t="b">
+        <v>0</v>
+      </c>
+      <c r="N34" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2123,15 +2331,21 @@
         <v>1</v>
       </c>
       <c r="I35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J35" t="b">
         <v>1</v>
       </c>
       <c r="K35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" t="b">
+        <v>1</v>
+      </c>
+      <c r="M35" t="b">
+        <v>0</v>
+      </c>
+      <c r="N35" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2163,15 +2377,21 @@
         <v>1</v>
       </c>
       <c r="I36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J36" t="b">
         <v>1</v>
       </c>
       <c r="K36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" t="b">
+        <v>1</v>
+      </c>
+      <c r="M36" t="b">
+        <v>0</v>
+      </c>
+      <c r="N36" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2203,15 +2423,21 @@
         <v>1</v>
       </c>
       <c r="I37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" t="b">
         <v>1</v>
       </c>
       <c r="K37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" t="b">
+        <v>1</v>
+      </c>
+      <c r="M37" t="b">
+        <v>0</v>
+      </c>
+      <c r="N37" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2243,15 +2469,21 @@
         <v>1</v>
       </c>
       <c r="I38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J38" t="b">
         <v>1</v>
       </c>
       <c r="K38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" t="b">
+        <v>1</v>
+      </c>
+      <c r="M38" t="b">
+        <v>0</v>
+      </c>
+      <c r="N38" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2283,15 +2515,21 @@
         <v>1</v>
       </c>
       <c r="I39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" t="b">
         <v>1</v>
       </c>
       <c r="K39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" t="b">
+        <v>1</v>
+      </c>
+      <c r="M39" t="b">
+        <v>0</v>
+      </c>
+      <c r="N39" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2323,15 +2561,21 @@
         <v>1</v>
       </c>
       <c r="I40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J40" t="b">
         <v>1</v>
       </c>
       <c r="K40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" t="b">
+        <v>1</v>
+      </c>
+      <c r="M40" t="b">
+        <v>0</v>
+      </c>
+      <c r="N40" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2363,15 +2607,21 @@
         <v>1</v>
       </c>
       <c r="I41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" t="b">
         <v>1</v>
       </c>
       <c r="K41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" t="b">
+        <v>1</v>
+      </c>
+      <c r="M41" t="b">
+        <v>0</v>
+      </c>
+      <c r="N41" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2403,15 +2653,21 @@
         <v>1</v>
       </c>
       <c r="I42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" t="b">
         <v>1</v>
       </c>
       <c r="K42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" t="b">
+        <v>1</v>
+      </c>
+      <c r="M42" t="b">
+        <v>0</v>
+      </c>
+      <c r="N42" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2443,15 +2699,21 @@
         <v>1</v>
       </c>
       <c r="I43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J43" t="b">
         <v>1</v>
       </c>
       <c r="K43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" t="b">
+        <v>1</v>
+      </c>
+      <c r="M43" t="b">
+        <v>0</v>
+      </c>
+      <c r="N43" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2483,15 +2745,21 @@
         <v>1</v>
       </c>
       <c r="I44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J44" t="b">
         <v>1</v>
       </c>
       <c r="K44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" t="b">
+        <v>1</v>
+      </c>
+      <c r="M44" t="b">
+        <v>0</v>
+      </c>
+      <c r="N44" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2523,15 +2791,21 @@
         <v>1</v>
       </c>
       <c r="I45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J45" t="b">
         <v>1</v>
       </c>
       <c r="K45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" t="b">
+        <v>1</v>
+      </c>
+      <c r="M45" t="b">
+        <v>0</v>
+      </c>
+      <c r="N45" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2563,15 +2837,21 @@
         <v>1</v>
       </c>
       <c r="I46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" t="b">
         <v>1</v>
       </c>
       <c r="K46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" t="b">
+        <v>1</v>
+      </c>
+      <c r="M46" t="b">
+        <v>0</v>
+      </c>
+      <c r="N46" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2603,15 +2883,21 @@
         <v>1</v>
       </c>
       <c r="I47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" t="b">
         <v>1</v>
       </c>
       <c r="K47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" t="b">
+        <v>1</v>
+      </c>
+      <c r="M47" t="b">
+        <v>0</v>
+      </c>
+      <c r="N47" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2643,15 +2929,21 @@
         <v>1</v>
       </c>
       <c r="I48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J48" t="b">
         <v>1</v>
       </c>
       <c r="K48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" t="b">
+        <v>1</v>
+      </c>
+      <c r="M48" t="b">
+        <v>0</v>
+      </c>
+      <c r="N48" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2683,15 +2975,21 @@
         <v>1</v>
       </c>
       <c r="I49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49" t="b">
         <v>1</v>
       </c>
       <c r="K49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" t="b">
+        <v>1</v>
+      </c>
+      <c r="M49" t="b">
+        <v>0</v>
+      </c>
+      <c r="N49" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2723,15 +3021,21 @@
         <v>1</v>
       </c>
       <c r="I50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J50" t="b">
         <v>1</v>
       </c>
       <c r="K50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" t="b">
+        <v>1</v>
+      </c>
+      <c r="M50" t="b">
+        <v>0</v>
+      </c>
+      <c r="N50" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2763,15 +3067,21 @@
         <v>1</v>
       </c>
       <c r="I51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J51" t="b">
         <v>1</v>
       </c>
       <c r="K51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" t="b">
+        <v>1</v>
+      </c>
+      <c r="M51" t="b">
+        <v>0</v>
+      </c>
+      <c r="N51" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2803,15 +3113,21 @@
         <v>1</v>
       </c>
       <c r="I52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J52" t="b">
         <v>1</v>
       </c>
       <c r="K52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" t="b">
+        <v>1</v>
+      </c>
+      <c r="M52" t="b">
+        <v>0</v>
+      </c>
+      <c r="N52" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2843,15 +3159,21 @@
         <v>1</v>
       </c>
       <c r="I53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J53" t="b">
         <v>1</v>
       </c>
       <c r="K53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" t="b">
+        <v>1</v>
+      </c>
+      <c r="M53" t="b">
+        <v>0</v>
+      </c>
+      <c r="N53" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2883,15 +3205,21 @@
         <v>1</v>
       </c>
       <c r="I54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J54" t="b">
         <v>1</v>
       </c>
       <c r="K54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" t="b">
+        <v>1</v>
+      </c>
+      <c r="M54" t="b">
+        <v>0</v>
+      </c>
+      <c r="N54" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2923,15 +3251,21 @@
         <v>1</v>
       </c>
       <c r="I55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J55" t="b">
         <v>1</v>
       </c>
       <c r="K55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" t="b">
+        <v>1</v>
+      </c>
+      <c r="M55" t="b">
+        <v>0</v>
+      </c>
+      <c r="N55" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2963,15 +3297,21 @@
         <v>1</v>
       </c>
       <c r="I56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" t="b">
         <v>1</v>
       </c>
       <c r="K56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" t="b">
+        <v>1</v>
+      </c>
+      <c r="M56" t="b">
+        <v>0</v>
+      </c>
+      <c r="N56" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3003,15 +3343,21 @@
         <v>1</v>
       </c>
       <c r="I57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J57" t="b">
         <v>1</v>
       </c>
       <c r="K57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" t="b">
+        <v>1</v>
+      </c>
+      <c r="M57" t="b">
+        <v>0</v>
+      </c>
+      <c r="N57" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3043,15 +3389,21 @@
         <v>1</v>
       </c>
       <c r="I58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J58" t="b">
         <v>1</v>
       </c>
       <c r="K58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" t="b">
+        <v>1</v>
+      </c>
+      <c r="M58" t="b">
+        <v>0</v>
+      </c>
+      <c r="N58" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3083,15 +3435,21 @@
         <v>1</v>
       </c>
       <c r="I59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J59" t="b">
         <v>1</v>
       </c>
       <c r="K59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" t="b">
+        <v>1</v>
+      </c>
+      <c r="M59" t="b">
+        <v>0</v>
+      </c>
+      <c r="N59" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3123,15 +3481,21 @@
         <v>1</v>
       </c>
       <c r="I60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J60" t="b">
         <v>1</v>
       </c>
       <c r="K60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" t="b">
+        <v>1</v>
+      </c>
+      <c r="M60" t="b">
+        <v>0</v>
+      </c>
+      <c r="N60" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3163,15 +3527,21 @@
         <v>1</v>
       </c>
       <c r="I61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J61" t="b">
         <v>1</v>
       </c>
       <c r="K61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" t="b">
+        <v>1</v>
+      </c>
+      <c r="M61" t="b">
+        <v>0</v>
+      </c>
+      <c r="N61" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3203,15 +3573,21 @@
         <v>1</v>
       </c>
       <c r="I62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J62" t="b">
         <v>1</v>
       </c>
       <c r="K62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" t="b">
+        <v>1</v>
+      </c>
+      <c r="M62" t="b">
+        <v>0</v>
+      </c>
+      <c r="N62" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3243,15 +3619,21 @@
         <v>1</v>
       </c>
       <c r="I63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J63" t="b">
         <v>1</v>
       </c>
       <c r="K63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" t="b">
+        <v>1</v>
+      </c>
+      <c r="M63" t="b">
+        <v>0</v>
+      </c>
+      <c r="N63" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3283,15 +3665,21 @@
         <v>1</v>
       </c>
       <c r="I64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J64" t="b">
         <v>1</v>
       </c>
       <c r="K64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" t="b">
+        <v>1</v>
+      </c>
+      <c r="M64" t="b">
+        <v>0</v>
+      </c>
+      <c r="N64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3323,15 +3711,21 @@
         <v>1</v>
       </c>
       <c r="I65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J65" t="b">
         <v>1</v>
       </c>
       <c r="K65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" t="b">
+        <v>1</v>
+      </c>
+      <c r="M65" t="b">
+        <v>0</v>
+      </c>
+      <c r="N65" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3363,15 +3757,21 @@
         <v>1</v>
       </c>
       <c r="I66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J66" t="b">
         <v>1</v>
       </c>
       <c r="K66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" t="b">
+        <v>1</v>
+      </c>
+      <c r="M66" t="b">
+        <v>0</v>
+      </c>
+      <c r="N66" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3403,15 +3803,21 @@
         <v>1</v>
       </c>
       <c r="I67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J67" t="b">
         <v>1</v>
       </c>
       <c r="K67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" t="b">
+        <v>1</v>
+      </c>
+      <c r="M67" t="b">
+        <v>0</v>
+      </c>
+      <c r="N67" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3443,15 +3849,21 @@
         <v>1</v>
       </c>
       <c r="I68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J68" t="b">
         <v>1</v>
       </c>
       <c r="K68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" t="b">
+        <v>1</v>
+      </c>
+      <c r="M68" t="b">
+        <v>0</v>
+      </c>
+      <c r="N68" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3483,15 +3895,21 @@
         <v>1</v>
       </c>
       <c r="I69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J69" t="b">
         <v>1</v>
       </c>
       <c r="K69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" t="b">
+        <v>1</v>
+      </c>
+      <c r="M69" t="b">
+        <v>0</v>
+      </c>
+      <c r="N69" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3523,15 +3941,21 @@
         <v>1</v>
       </c>
       <c r="I70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J70" t="b">
         <v>1</v>
       </c>
       <c r="K70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" t="b">
+        <v>1</v>
+      </c>
+      <c r="M70" t="b">
+        <v>0</v>
+      </c>
+      <c r="N70" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3563,15 +3987,21 @@
         <v>1</v>
       </c>
       <c r="I71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J71" t="b">
         <v>1</v>
       </c>
       <c r="K71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" t="b">
+        <v>1</v>
+      </c>
+      <c r="M71" t="b">
+        <v>0</v>
+      </c>
+      <c r="N71" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3603,15 +4033,21 @@
         <v>1</v>
       </c>
       <c r="I72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J72" t="b">
         <v>1</v>
       </c>
       <c r="K72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" t="b">
+        <v>1</v>
+      </c>
+      <c r="M72" t="b">
+        <v>0</v>
+      </c>
+      <c r="N72" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3643,15 +4079,21 @@
         <v>1</v>
       </c>
       <c r="I73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J73" t="b">
         <v>1</v>
       </c>
       <c r="K73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" t="b">
+        <v>1</v>
+      </c>
+      <c r="M73" t="b">
+        <v>0</v>
+      </c>
+      <c r="N73" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3683,15 +4125,21 @@
         <v>1</v>
       </c>
       <c r="I74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J74" t="b">
         <v>1</v>
       </c>
       <c r="K74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" t="b">
+        <v>1</v>
+      </c>
+      <c r="M74" t="b">
+        <v>0</v>
+      </c>
+      <c r="N74" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3723,15 +4171,21 @@
         <v>1</v>
       </c>
       <c r="I75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J75" t="b">
         <v>1</v>
       </c>
       <c r="K75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" t="b">
+        <v>1</v>
+      </c>
+      <c r="M75" t="b">
+        <v>0</v>
+      </c>
+      <c r="N75" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3763,15 +4217,21 @@
         <v>1</v>
       </c>
       <c r="I76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J76" t="b">
         <v>1</v>
       </c>
       <c r="K76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" t="b">
+        <v>1</v>
+      </c>
+      <c r="M76" t="b">
+        <v>0</v>
+      </c>
+      <c r="N76" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3803,15 +4263,21 @@
         <v>1</v>
       </c>
       <c r="I77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J77" t="b">
         <v>1</v>
       </c>
       <c r="K77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" t="b">
+        <v>1</v>
+      </c>
+      <c r="M77" t="b">
+        <v>0</v>
+      </c>
+      <c r="N77" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3843,15 +4309,21 @@
         <v>1</v>
       </c>
       <c r="I78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J78" t="b">
         <v>1</v>
       </c>
       <c r="K78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" t="b">
+        <v>1</v>
+      </c>
+      <c r="M78" t="b">
+        <v>0</v>
+      </c>
+      <c r="N78" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3883,15 +4355,21 @@
         <v>1</v>
       </c>
       <c r="I79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J79" t="b">
         <v>1</v>
       </c>
       <c r="K79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" t="b">
+        <v>1</v>
+      </c>
+      <c r="M79" t="b">
+        <v>0</v>
+      </c>
+      <c r="N79" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3923,15 +4401,21 @@
         <v>1</v>
       </c>
       <c r="I80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J80" t="b">
         <v>1</v>
       </c>
       <c r="K80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" t="b">
+        <v>1</v>
+      </c>
+      <c r="M80" t="b">
+        <v>0</v>
+      </c>
+      <c r="N80" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3963,15 +4447,21 @@
         <v>1</v>
       </c>
       <c r="I81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J81" t="b">
         <v>1</v>
       </c>
       <c r="K81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L81" t="b">
+        <v>1</v>
+      </c>
+      <c r="M81" t="b">
+        <v>0</v>
+      </c>
+      <c r="N81" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4003,15 +4493,21 @@
         <v>0</v>
       </c>
       <c r="I82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J82" t="b">
         <v>0</v>
       </c>
       <c r="K82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" t="b">
+        <v>0</v>
+      </c>
+      <c r="M82" t="b">
+        <v>0</v>
+      </c>
+      <c r="N82" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4043,15 +4539,21 @@
         <v>0</v>
       </c>
       <c r="I83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J83" t="b">
         <v>0</v>
       </c>
       <c r="K83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" t="b">
+        <v>0</v>
+      </c>
+      <c r="M83" t="b">
+        <v>0</v>
+      </c>
+      <c r="N83" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4083,15 +4585,21 @@
         <v>0</v>
       </c>
       <c r="I84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J84" t="b">
         <v>0</v>
       </c>
       <c r="K84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" t="b">
+        <v>0</v>
+      </c>
+      <c r="M84" t="b">
+        <v>0</v>
+      </c>
+      <c r="N84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4126,12 +4634,18 @@
         <v>1</v>
       </c>
       <c r="J85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" t="b">
+        <v>0</v>
+      </c>
+      <c r="M85" t="b">
+        <v>0</v>
+      </c>
+      <c r="N85" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4166,12 +4680,18 @@
         <v>1</v>
       </c>
       <c r="J86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" t="b">
+        <v>0</v>
+      </c>
+      <c r="M86" t="b">
+        <v>0</v>
+      </c>
+      <c r="N86" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4206,12 +4726,18 @@
         <v>1</v>
       </c>
       <c r="J87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" t="b">
+        <v>0</v>
+      </c>
+      <c r="M87" t="b">
+        <v>0</v>
+      </c>
+      <c r="N87" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4246,12 +4772,18 @@
         <v>1</v>
       </c>
       <c r="J88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" t="b">
+        <v>0</v>
+      </c>
+      <c r="M88" t="b">
+        <v>0</v>
+      </c>
+      <c r="N88" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4286,12 +4818,18 @@
         <v>1</v>
       </c>
       <c r="J89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" t="b">
+        <v>0</v>
+      </c>
+      <c r="M89" t="b">
+        <v>0</v>
+      </c>
+      <c r="N89" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4326,12 +4864,18 @@
         <v>1</v>
       </c>
       <c r="J90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L90" t="b">
+        <v>0</v>
+      </c>
+      <c r="M90" t="b">
+        <v>0</v>
+      </c>
+      <c r="N90" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4366,12 +4910,18 @@
         <v>1</v>
       </c>
       <c r="J91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" t="b">
+        <v>0</v>
+      </c>
+      <c r="M91" t="b">
+        <v>0</v>
+      </c>
+      <c r="N91" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4406,12 +4956,18 @@
         <v>1</v>
       </c>
       <c r="J92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" t="b">
+        <v>0</v>
+      </c>
+      <c r="M92" t="b">
+        <v>0</v>
+      </c>
+      <c r="N92" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4446,12 +5002,18 @@
         <v>1</v>
       </c>
       <c r="J93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" t="b">
+        <v>0</v>
+      </c>
+      <c r="M93" t="b">
+        <v>0</v>
+      </c>
+      <c r="N93" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4486,12 +5048,18 @@
         <v>1</v>
       </c>
       <c r="J94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" t="b">
+        <v>0</v>
+      </c>
+      <c r="M94" t="b">
+        <v>0</v>
+      </c>
+      <c r="N94" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4526,12 +5094,18 @@
         <v>1</v>
       </c>
       <c r="J95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L95" t="b">
+        <v>0</v>
+      </c>
+      <c r="M95" t="b">
+        <v>0</v>
+      </c>
+      <c r="N95" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4569,9 +5143,15 @@
         <v>1</v>
       </c>
       <c r="K96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" t="b">
+        <v>1</v>
+      </c>
+      <c r="M96" t="b">
+        <v>0</v>
+      </c>
+      <c r="N96" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4614,6 +5194,12 @@
       <c r="L97" t="b">
         <v>1</v>
       </c>
+      <c r="M97" t="b">
+        <v>1</v>
+      </c>
+      <c r="N97" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4654,6 +5240,12 @@
       <c r="L98" t="b">
         <v>1</v>
       </c>
+      <c r="M98" t="b">
+        <v>1</v>
+      </c>
+      <c r="N98" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4694,6 +5286,12 @@
       <c r="L99" t="b">
         <v>1</v>
       </c>
+      <c r="M99" t="b">
+        <v>1</v>
+      </c>
+      <c r="N99" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4734,6 +5332,12 @@
       <c r="L100" t="b">
         <v>1</v>
       </c>
+      <c r="M100" t="b">
+        <v>1</v>
+      </c>
+      <c r="N100" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4774,6 +5378,12 @@
       <c r="L101" t="b">
         <v>1</v>
       </c>
+      <c r="M101" t="b">
+        <v>1</v>
+      </c>
+      <c r="N101" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4814,6 +5424,12 @@
       <c r="L102" t="b">
         <v>1</v>
       </c>
+      <c r="M102" t="b">
+        <v>1</v>
+      </c>
+      <c r="N102" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4854,6 +5470,12 @@
       <c r="L103" t="b">
         <v>1</v>
       </c>
+      <c r="M103" t="b">
+        <v>1</v>
+      </c>
+      <c r="N103" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4894,6 +5516,12 @@
       <c r="L104" t="b">
         <v>1</v>
       </c>
+      <c r="M104" t="b">
+        <v>1</v>
+      </c>
+      <c r="N104" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4934,6 +5562,12 @@
       <c r="L105" t="b">
         <v>1</v>
       </c>
+      <c r="M105" t="b">
+        <v>1</v>
+      </c>
+      <c r="N105" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4974,6 +5608,12 @@
       <c r="L106" t="b">
         <v>1</v>
       </c>
+      <c r="M106" t="b">
+        <v>1</v>
+      </c>
+      <c r="N106" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5014,6 +5654,12 @@
       <c r="L107" t="b">
         <v>1</v>
       </c>
+      <c r="M107" t="b">
+        <v>1</v>
+      </c>
+      <c r="N107" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5054,6 +5700,12 @@
       <c r="L108" t="b">
         <v>1</v>
       </c>
+      <c r="M108" t="b">
+        <v>1</v>
+      </c>
+      <c r="N108" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5094,6 +5746,12 @@
       <c r="L109" t="b">
         <v>1</v>
       </c>
+      <c r="M109" t="b">
+        <v>1</v>
+      </c>
+      <c r="N109" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5134,6 +5792,12 @@
       <c r="L110" t="b">
         <v>1</v>
       </c>
+      <c r="M110" t="b">
+        <v>1</v>
+      </c>
+      <c r="N110" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5174,6 +5838,12 @@
       <c r="L111" t="b">
         <v>1</v>
       </c>
+      <c r="M111" t="b">
+        <v>1</v>
+      </c>
+      <c r="N111" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5203,15 +5873,21 @@
         <v>0</v>
       </c>
       <c r="I112" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J112" t="b">
         <v>0</v>
       </c>
       <c r="K112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L112" t="b">
+        <v>0</v>
+      </c>
+      <c r="M112" t="b">
+        <v>0</v>
+      </c>
+      <c r="N112" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5243,15 +5919,21 @@
         <v>0</v>
       </c>
       <c r="I113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J113" t="b">
         <v>0</v>
       </c>
       <c r="K113" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L113" t="b">
+        <v>0</v>
+      </c>
+      <c r="M113" t="b">
+        <v>0</v>
+      </c>
+      <c r="N113" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5283,15 +5965,21 @@
         <v>0</v>
       </c>
       <c r="I114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J114" t="b">
         <v>0</v>
       </c>
       <c r="K114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L114" t="b">
+        <v>0</v>
+      </c>
+      <c r="M114" t="b">
+        <v>0</v>
+      </c>
+      <c r="N114" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5323,15 +6011,21 @@
         <v>0</v>
       </c>
       <c r="I115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J115" t="b">
         <v>0</v>
       </c>
       <c r="K115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L115" t="b">
+        <v>0</v>
+      </c>
+      <c r="M115" t="b">
+        <v>0</v>
+      </c>
+      <c r="N115" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5363,15 +6057,21 @@
         <v>0</v>
       </c>
       <c r="I116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J116" t="b">
         <v>0</v>
       </c>
       <c r="K116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L116" t="b">
+        <v>0</v>
+      </c>
+      <c r="M116" t="b">
+        <v>0</v>
+      </c>
+      <c r="N116" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5403,15 +6103,21 @@
         <v>0</v>
       </c>
       <c r="I117" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J117" t="b">
         <v>0</v>
       </c>
       <c r="K117" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L117" t="b">
+        <v>0</v>
+      </c>
+      <c r="M117" t="b">
+        <v>0</v>
+      </c>
+      <c r="N117" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5443,15 +6149,21 @@
         <v>0</v>
       </c>
       <c r="I118" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J118" t="b">
         <v>0</v>
       </c>
       <c r="K118" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L118" t="b">
+        <v>0</v>
+      </c>
+      <c r="M118" t="b">
+        <v>0</v>
+      </c>
+      <c r="N118" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5483,15 +6195,21 @@
         <v>0</v>
       </c>
       <c r="I119" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J119" t="b">
         <v>0</v>
       </c>
       <c r="K119" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L119" t="b">
+        <v>0</v>
+      </c>
+      <c r="M119" t="b">
+        <v>0</v>
+      </c>
+      <c r="N119" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5523,15 +6241,21 @@
         <v>0</v>
       </c>
       <c r="I120" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J120" t="b">
         <v>0</v>
       </c>
       <c r="K120" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L120" t="b">
+        <v>0</v>
+      </c>
+      <c r="M120" t="b">
+        <v>0</v>
+      </c>
+      <c r="N120" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5563,15 +6287,21 @@
         <v>0</v>
       </c>
       <c r="I121" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J121" t="b">
         <v>0</v>
       </c>
       <c r="K121" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L121" t="b">
+        <v>0</v>
+      </c>
+      <c r="M121" t="b">
+        <v>0</v>
+      </c>
+      <c r="N121" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5603,15 +6333,21 @@
         <v>0</v>
       </c>
       <c r="I122" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J122" t="b">
         <v>0</v>
       </c>
       <c r="K122" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L122" t="b">
+        <v>0</v>
+      </c>
+      <c r="M122" t="b">
+        <v>0</v>
+      </c>
+      <c r="N122" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5643,15 +6379,21 @@
         <v>0</v>
       </c>
       <c r="I123" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J123" t="b">
         <v>0</v>
       </c>
       <c r="K123" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L123" t="b">
+        <v>0</v>
+      </c>
+      <c r="M123" t="b">
+        <v>0</v>
+      </c>
+      <c r="N123" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5683,15 +6425,21 @@
         <v>0</v>
       </c>
       <c r="I124" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J124" t="b">
         <v>0</v>
       </c>
       <c r="K124" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L124" t="b">
+        <v>0</v>
+      </c>
+      <c r="M124" t="b">
+        <v>0</v>
+      </c>
+      <c r="N124" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5723,15 +6471,21 @@
         <v>0</v>
       </c>
       <c r="I125" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J125" t="b">
         <v>0</v>
       </c>
       <c r="K125" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L125" t="b">
+        <v>0</v>
+      </c>
+      <c r="M125" t="b">
+        <v>0</v>
+      </c>
+      <c r="N125" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5763,15 +6517,21 @@
         <v>1</v>
       </c>
       <c r="I126" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J126" t="b">
         <v>1</v>
       </c>
       <c r="K126" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L126" t="b">
+        <v>1</v>
+      </c>
+      <c r="M126" t="b">
+        <v>0</v>
+      </c>
+      <c r="N126" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5803,15 +6563,21 @@
         <v>1</v>
       </c>
       <c r="I127" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J127" t="b">
         <v>1</v>
       </c>
       <c r="K127" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L127" t="b">
+        <v>1</v>
+      </c>
+      <c r="M127" t="b">
+        <v>0</v>
+      </c>
+      <c r="N127" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5843,15 +6609,21 @@
         <v>1</v>
       </c>
       <c r="I128" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J128" t="b">
         <v>1</v>
       </c>
       <c r="K128" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L128" t="b">
+        <v>1</v>
+      </c>
+      <c r="M128" t="b">
+        <v>0</v>
+      </c>
+      <c r="N128" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5883,15 +6655,21 @@
         <v>1</v>
       </c>
       <c r="I129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J129" t="b">
         <v>1</v>
       </c>
       <c r="K129" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L129" t="b">
+        <v>1</v>
+      </c>
+      <c r="M129" t="b">
+        <v>0</v>
+      </c>
+      <c r="N129" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5923,15 +6701,21 @@
         <v>1</v>
       </c>
       <c r="I130" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J130" t="b">
         <v>1</v>
       </c>
       <c r="K130" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L130" t="b">
+        <v>1</v>
+      </c>
+      <c r="M130" t="b">
+        <v>0</v>
+      </c>
+      <c r="N130" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5963,15 +6747,21 @@
         <v>1</v>
       </c>
       <c r="I131" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J131" t="b">
         <v>1</v>
       </c>
       <c r="K131" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L131" t="b">
+        <v>1</v>
+      </c>
+      <c r="M131" t="b">
+        <v>0</v>
+      </c>
+      <c r="N131" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6003,15 +6793,21 @@
         <v>1</v>
       </c>
       <c r="I132" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J132" t="b">
         <v>1</v>
       </c>
       <c r="K132" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L132" t="b">
+        <v>1</v>
+      </c>
+      <c r="M132" t="b">
+        <v>0</v>
+      </c>
+      <c r="N132" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6043,15 +6839,21 @@
         <v>1</v>
       </c>
       <c r="I133" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J133" t="b">
         <v>1</v>
       </c>
       <c r="K133" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L133" t="b">
+        <v>1</v>
+      </c>
+      <c r="M133" t="b">
+        <v>0</v>
+      </c>
+      <c r="N133" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6083,15 +6885,21 @@
         <v>1</v>
       </c>
       <c r="I134" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J134" t="b">
         <v>1</v>
       </c>
       <c r="K134" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L134" t="b">
+        <v>1</v>
+      </c>
+      <c r="M134" t="b">
+        <v>0</v>
+      </c>
+      <c r="N134" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6123,15 +6931,21 @@
         <v>1</v>
       </c>
       <c r="I135" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J135" t="b">
         <v>1</v>
       </c>
       <c r="K135" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L135" t="b">
+        <v>1</v>
+      </c>
+      <c r="M135" t="b">
+        <v>0</v>
+      </c>
+      <c r="N135" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6163,15 +6977,21 @@
         <v>1</v>
       </c>
       <c r="I136" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J136" t="b">
         <v>1</v>
       </c>
       <c r="K136" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L136" t="b">
+        <v>1</v>
+      </c>
+      <c r="M136" t="b">
+        <v>0</v>
+      </c>
+      <c r="N136" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6203,15 +7023,21 @@
         <v>1</v>
       </c>
       <c r="I137" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J137" t="b">
         <v>1</v>
       </c>
       <c r="K137" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L137" t="b">
+        <v>1</v>
+      </c>
+      <c r="M137" t="b">
+        <v>0</v>
+      </c>
+      <c r="N137" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6243,15 +7069,21 @@
         <v>1</v>
       </c>
       <c r="I138" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J138" t="b">
         <v>1</v>
       </c>
       <c r="K138" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L138" t="b">
+        <v>1</v>
+      </c>
+      <c r="M138" t="b">
+        <v>0</v>
+      </c>
+      <c r="N138" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6283,15 +7115,21 @@
         <v>1</v>
       </c>
       <c r="I139" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J139" t="b">
         <v>1</v>
       </c>
       <c r="K139" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L139" t="b">
+        <v>1</v>
+      </c>
+      <c r="M139" t="b">
+        <v>0</v>
+      </c>
+      <c r="N139" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6323,15 +7161,21 @@
         <v>1</v>
       </c>
       <c r="I140" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J140" t="b">
         <v>1</v>
       </c>
       <c r="K140" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L140" t="b">
+        <v>1</v>
+      </c>
+      <c r="M140" t="b">
+        <v>0</v>
+      </c>
+      <c r="N140" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6363,15 +7207,21 @@
         <v>1</v>
       </c>
       <c r="I141" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J141" t="b">
         <v>1</v>
       </c>
       <c r="K141" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L141" t="b">
+        <v>1</v>
+      </c>
+      <c r="M141" t="b">
+        <v>0</v>
+      </c>
+      <c r="N141" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6403,15 +7253,21 @@
         <v>1</v>
       </c>
       <c r="I142" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J142" t="b">
         <v>1</v>
       </c>
       <c r="K142" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L142" t="b">
+        <v>1</v>
+      </c>
+      <c r="M142" t="b">
+        <v>0</v>
+      </c>
+      <c r="N142" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6443,15 +7299,21 @@
         <v>1</v>
       </c>
       <c r="I143" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J143" t="b">
         <v>1</v>
       </c>
       <c r="K143" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L143" t="b">
+        <v>1</v>
+      </c>
+      <c r="M143" t="b">
+        <v>0</v>
+      </c>
+      <c r="N143" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6483,15 +7345,21 @@
         <v>1</v>
       </c>
       <c r="I144" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J144" t="b">
         <v>1</v>
       </c>
       <c r="K144" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L144" t="b">
+        <v>1</v>
+      </c>
+      <c r="M144" t="b">
+        <v>0</v>
+      </c>
+      <c r="N144" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6523,15 +7391,21 @@
         <v>1</v>
       </c>
       <c r="I145" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J145" t="b">
         <v>1</v>
       </c>
       <c r="K145" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L145" t="b">
+        <v>1</v>
+      </c>
+      <c r="M145" t="b">
+        <v>0</v>
+      </c>
+      <c r="N145" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6563,15 +7437,21 @@
         <v>1</v>
       </c>
       <c r="I146" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J146" t="b">
         <v>1</v>
       </c>
       <c r="K146" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L146" t="b">
+        <v>1</v>
+      </c>
+      <c r="M146" t="b">
+        <v>0</v>
+      </c>
+      <c r="N146" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6603,15 +7483,21 @@
         <v>1</v>
       </c>
       <c r="I147" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J147" t="b">
         <v>1</v>
       </c>
       <c r="K147" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L147" t="b">
+        <v>1</v>
+      </c>
+      <c r="M147" t="b">
+        <v>0</v>
+      </c>
+      <c r="N147" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6643,15 +7529,21 @@
         <v>1</v>
       </c>
       <c r="I148" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J148" t="b">
         <v>1</v>
       </c>
       <c r="K148" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L148" t="b">
+        <v>1</v>
+      </c>
+      <c r="M148" t="b">
+        <v>0</v>
+      </c>
+      <c r="N148" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6683,15 +7575,21 @@
         <v>1</v>
       </c>
       <c r="I149" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J149" t="b">
         <v>1</v>
       </c>
       <c r="K149" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L149" t="b">
+        <v>1</v>
+      </c>
+      <c r="M149" t="b">
+        <v>0</v>
+      </c>
+      <c r="N149" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6723,15 +7621,21 @@
         <v>1</v>
       </c>
       <c r="I150" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J150" t="b">
         <v>1</v>
       </c>
       <c r="K150" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L150" t="b">
+        <v>1</v>
+      </c>
+      <c r="M150" t="b">
+        <v>0</v>
+      </c>
+      <c r="N150" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6763,15 +7667,21 @@
         <v>1</v>
       </c>
       <c r="I151" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J151" t="b">
         <v>1</v>
       </c>
       <c r="K151" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L151" t="b">
+        <v>1</v>
+      </c>
+      <c r="M151" t="b">
+        <v>0</v>
+      </c>
+      <c r="N151" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6803,15 +7713,21 @@
         <v>1</v>
       </c>
       <c r="I152" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J152" t="b">
         <v>1</v>
       </c>
       <c r="K152" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L152" t="b">
+        <v>1</v>
+      </c>
+      <c r="M152" t="b">
+        <v>0</v>
+      </c>
+      <c r="N152" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6843,15 +7759,21 @@
         <v>1</v>
       </c>
       <c r="I153" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J153" t="b">
         <v>1</v>
       </c>
       <c r="K153" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L153" t="b">
+        <v>1</v>
+      </c>
+      <c r="M153" t="b">
+        <v>0</v>
+      </c>
+      <c r="N153" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6883,15 +7805,21 @@
         <v>1</v>
       </c>
       <c r="I154" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J154" t="b">
         <v>1</v>
       </c>
       <c r="K154" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L154" t="b">
+        <v>1</v>
+      </c>
+      <c r="M154" t="b">
+        <v>0</v>
+      </c>
+      <c r="N154" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6923,15 +7851,21 @@
         <v>1</v>
       </c>
       <c r="I155" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J155" t="b">
         <v>1</v>
       </c>
       <c r="K155" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L155" t="b">
+        <v>1</v>
+      </c>
+      <c r="M155" t="b">
+        <v>0</v>
+      </c>
+      <c r="N155" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6963,15 +7897,21 @@
         <v>1</v>
       </c>
       <c r="I156" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J156" t="b">
         <v>1</v>
       </c>
       <c r="K156" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L156" t="b">
+        <v>1</v>
+      </c>
+      <c r="M156" t="b">
+        <v>0</v>
+      </c>
+      <c r="N156" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7003,15 +7943,21 @@
         <v>1</v>
       </c>
       <c r="I157" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J157" t="b">
         <v>1</v>
       </c>
       <c r="K157" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L157" t="b">
+        <v>1</v>
+      </c>
+      <c r="M157" t="b">
+        <v>0</v>
+      </c>
+      <c r="N157" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7043,15 +7989,21 @@
         <v>1</v>
       </c>
       <c r="I158" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J158" t="b">
         <v>1</v>
       </c>
       <c r="K158" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L158" t="b">
+        <v>1</v>
+      </c>
+      <c r="M158" t="b">
+        <v>0</v>
+      </c>
+      <c r="N158" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7083,15 +8035,21 @@
         <v>1</v>
       </c>
       <c r="I159" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J159" t="b">
         <v>1</v>
       </c>
       <c r="K159" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L159" t="b">
+        <v>1</v>
+      </c>
+      <c r="M159" t="b">
+        <v>0</v>
+      </c>
+      <c r="N159" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7123,15 +8081,21 @@
         <v>1</v>
       </c>
       <c r="I160" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J160" t="b">
         <v>1</v>
       </c>
       <c r="K160" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L160" t="b">
+        <v>1</v>
+      </c>
+      <c r="M160" t="b">
+        <v>0</v>
+      </c>
+      <c r="N160" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7163,15 +8127,21 @@
         <v>1</v>
       </c>
       <c r="I161" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J161" t="b">
         <v>1</v>
       </c>
       <c r="K161" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L161" t="b">
+        <v>1</v>
+      </c>
+      <c r="M161" t="b">
+        <v>0</v>
+      </c>
+      <c r="N161" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7203,15 +8173,21 @@
         <v>1</v>
       </c>
       <c r="I162" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J162" t="b">
         <v>1</v>
       </c>
       <c r="K162" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L162" t="b">
+        <v>1</v>
+      </c>
+      <c r="M162" t="b">
+        <v>0</v>
+      </c>
+      <c r="N162" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7243,15 +8219,21 @@
         <v>1</v>
       </c>
       <c r="I163" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J163" t="b">
         <v>1</v>
       </c>
       <c r="K163" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L163" t="b">
+        <v>1</v>
+      </c>
+      <c r="M163" t="b">
+        <v>0</v>
+      </c>
+      <c r="N163" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7283,15 +8265,21 @@
         <v>1</v>
       </c>
       <c r="I164" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J164" t="b">
         <v>1</v>
       </c>
       <c r="K164" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L164" t="b">
+        <v>1</v>
+      </c>
+      <c r="M164" t="b">
+        <v>0</v>
+      </c>
+      <c r="N164" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7323,15 +8311,21 @@
         <v>1</v>
       </c>
       <c r="I165" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J165" t="b">
         <v>1</v>
       </c>
       <c r="K165" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L165" t="b">
+        <v>1</v>
+      </c>
+      <c r="M165" t="b">
+        <v>0</v>
+      </c>
+      <c r="N165" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7363,15 +8357,21 @@
         <v>1</v>
       </c>
       <c r="I166" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J166" t="b">
         <v>1</v>
       </c>
       <c r="K166" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L166" t="b">
+        <v>1</v>
+      </c>
+      <c r="M166" t="b">
+        <v>0</v>
+      </c>
+      <c r="N166" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7403,15 +8403,21 @@
         <v>1</v>
       </c>
       <c r="I167" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J167" t="b">
         <v>1</v>
       </c>
       <c r="K167" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L167" t="b">
+        <v>1</v>
+      </c>
+      <c r="M167" t="b">
+        <v>0</v>
+      </c>
+      <c r="N167" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7443,15 +8449,21 @@
         <v>1</v>
       </c>
       <c r="I168" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J168" t="b">
         <v>1</v>
       </c>
       <c r="K168" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L168" t="b">
+        <v>1</v>
+      </c>
+      <c r="M168" t="b">
+        <v>0</v>
+      </c>
+      <c r="N168" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7483,15 +8495,21 @@
         <v>1</v>
       </c>
       <c r="I169" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J169" t="b">
         <v>1</v>
       </c>
       <c r="K169" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L169" t="b">
+        <v>1</v>
+      </c>
+      <c r="M169" t="b">
+        <v>0</v>
+      </c>
+      <c r="N169" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7523,15 +8541,21 @@
         <v>1</v>
       </c>
       <c r="I170" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J170" t="b">
         <v>1</v>
       </c>
       <c r="K170" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L170" t="b">
+        <v>1</v>
+      </c>
+      <c r="M170" t="b">
+        <v>0</v>
+      </c>
+      <c r="N170" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7563,15 +8587,21 @@
         <v>1</v>
       </c>
       <c r="I171" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J171" t="b">
         <v>1</v>
       </c>
       <c r="K171" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L171" t="b">
+        <v>1</v>
+      </c>
+      <c r="M171" t="b">
+        <v>0</v>
+      </c>
+      <c r="N171" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7603,15 +8633,21 @@
         <v>1</v>
       </c>
       <c r="I172" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J172" t="b">
         <v>1</v>
       </c>
       <c r="K172" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L172" t="b">
+        <v>1</v>
+      </c>
+      <c r="M172" t="b">
+        <v>0</v>
+      </c>
+      <c r="N172" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7643,15 +8679,21 @@
         <v>1</v>
       </c>
       <c r="I173" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J173" t="b">
         <v>1</v>
       </c>
       <c r="K173" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L173" t="b">
+        <v>1</v>
+      </c>
+      <c r="M173" t="b">
+        <v>0</v>
+      </c>
+      <c r="N173" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7683,15 +8725,21 @@
         <v>1</v>
       </c>
       <c r="I174" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J174" t="b">
         <v>1</v>
       </c>
       <c r="K174" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L174" t="b">
+        <v>1</v>
+      </c>
+      <c r="M174" t="b">
+        <v>0</v>
+      </c>
+      <c r="N174" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7723,15 +8771,21 @@
         <v>1</v>
       </c>
       <c r="I175" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J175" t="b">
         <v>1</v>
       </c>
       <c r="K175" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L175" t="b">
+        <v>1</v>
+      </c>
+      <c r="M175" t="b">
+        <v>0</v>
+      </c>
+      <c r="N175" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7763,15 +8817,21 @@
         <v>1</v>
       </c>
       <c r="I176" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J176" t="b">
         <v>1</v>
       </c>
       <c r="K176" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L176" t="b">
+        <v>1</v>
+      </c>
+      <c r="M176" t="b">
+        <v>0</v>
+      </c>
+      <c r="N176" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7803,15 +8863,21 @@
         <v>1</v>
       </c>
       <c r="I177" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J177" t="b">
         <v>1</v>
       </c>
       <c r="K177" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L177" t="b">
+        <v>1</v>
+      </c>
+      <c r="M177" t="b">
+        <v>0</v>
+      </c>
+      <c r="N177" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7843,15 +8909,21 @@
         <v>1</v>
       </c>
       <c r="I178" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J178" t="b">
         <v>1</v>
       </c>
       <c r="K178" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L178" t="b">
+        <v>1</v>
+      </c>
+      <c r="M178" t="b">
+        <v>0</v>
+      </c>
+      <c r="N178" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7883,15 +8955,21 @@
         <v>1</v>
       </c>
       <c r="I179" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J179" t="b">
         <v>1</v>
       </c>
       <c r="K179" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L179" t="b">
+        <v>1</v>
+      </c>
+      <c r="M179" t="b">
+        <v>0</v>
+      </c>
+      <c r="N179" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7923,15 +9001,21 @@
         <v>1</v>
       </c>
       <c r="I180" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J180" t="b">
         <v>1</v>
       </c>
       <c r="K180" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L180" t="b">
+        <v>1</v>
+      </c>
+      <c r="M180" t="b">
+        <v>0</v>
+      </c>
+      <c r="N180" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7963,15 +9047,21 @@
         <v>1</v>
       </c>
       <c r="I181" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J181" t="b">
         <v>1</v>
       </c>
       <c r="K181" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L181" t="b">
+        <v>1</v>
+      </c>
+      <c r="M181" t="b">
+        <v>0</v>
+      </c>
+      <c r="N181" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8003,15 +9093,21 @@
         <v>1</v>
       </c>
       <c r="I182" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J182" t="b">
         <v>1</v>
       </c>
       <c r="K182" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L182" t="b">
+        <v>1</v>
+      </c>
+      <c r="M182" t="b">
+        <v>0</v>
+      </c>
+      <c r="N182" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8043,15 +9139,21 @@
         <v>1</v>
       </c>
       <c r="I183" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J183" t="b">
         <v>1</v>
       </c>
       <c r="K183" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L183" t="b">
+        <v>1</v>
+      </c>
+      <c r="M183" t="b">
+        <v>0</v>
+      </c>
+      <c r="N183" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8083,15 +9185,21 @@
         <v>1</v>
       </c>
       <c r="I184" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J184" t="b">
         <v>1</v>
       </c>
       <c r="K184" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L184" t="b">
+        <v>1</v>
+      </c>
+      <c r="M184" t="b">
+        <v>0</v>
+      </c>
+      <c r="N184" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8123,15 +9231,21 @@
         <v>1</v>
       </c>
       <c r="I185" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J185" t="b">
         <v>1</v>
       </c>
       <c r="K185" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L185" t="b">
+        <v>1</v>
+      </c>
+      <c r="M185" t="b">
+        <v>0</v>
+      </c>
+      <c r="N185" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8163,15 +9277,21 @@
         <v>1</v>
       </c>
       <c r="I186" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J186" t="b">
         <v>1</v>
       </c>
       <c r="K186" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L186" t="b">
+        <v>1</v>
+      </c>
+      <c r="M186" t="b">
+        <v>0</v>
+      </c>
+      <c r="N186" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8203,15 +9323,21 @@
         <v>1</v>
       </c>
       <c r="I187" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J187" t="b">
         <v>1</v>
       </c>
       <c r="K187" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L187" t="b">
+        <v>1</v>
+      </c>
+      <c r="M187" t="b">
+        <v>0</v>
+      </c>
+      <c r="N187" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8243,15 +9369,21 @@
         <v>1</v>
       </c>
       <c r="I188" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J188" t="b">
         <v>1</v>
       </c>
       <c r="K188" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L188" t="b">
+        <v>1</v>
+      </c>
+      <c r="M188" t="b">
+        <v>0</v>
+      </c>
+      <c r="N188" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8283,15 +9415,21 @@
         <v>1</v>
       </c>
       <c r="I189" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J189" t="b">
         <v>1</v>
       </c>
       <c r="K189" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L189" t="b">
+        <v>1</v>
+      </c>
+      <c r="M189" t="b">
+        <v>0</v>
+      </c>
+      <c r="N189" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8323,15 +9461,21 @@
         <v>1</v>
       </c>
       <c r="I190" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J190" t="b">
         <v>1</v>
       </c>
       <c r="K190" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L190" t="b">
+        <v>1</v>
+      </c>
+      <c r="M190" t="b">
+        <v>0</v>
+      </c>
+      <c r="N190" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8363,15 +9507,21 @@
         <v>1</v>
       </c>
       <c r="I191" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J191" t="b">
         <v>1</v>
       </c>
       <c r="K191" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L191" t="b">
+        <v>1</v>
+      </c>
+      <c r="M191" t="b">
+        <v>0</v>
+      </c>
+      <c r="N191" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8403,15 +9553,21 @@
         <v>0</v>
       </c>
       <c r="I192" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J192" t="b">
         <v>0</v>
       </c>
       <c r="K192" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L192" t="b">
+        <v>0</v>
+      </c>
+      <c r="M192" t="b">
+        <v>0</v>
+      </c>
+      <c r="N192" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8443,15 +9599,21 @@
         <v>0</v>
       </c>
       <c r="I193" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J193" t="b">
         <v>0</v>
       </c>
       <c r="K193" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L193" t="b">
+        <v>0</v>
+      </c>
+      <c r="M193" t="b">
+        <v>0</v>
+      </c>
+      <c r="N193" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8483,15 +9645,21 @@
         <v>0</v>
       </c>
       <c r="I194" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J194" t="b">
         <v>0</v>
       </c>
       <c r="K194" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L194" t="b">
+        <v>0</v>
+      </c>
+      <c r="M194" t="b">
+        <v>0</v>
+      </c>
+      <c r="N194" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8526,12 +9694,18 @@
         <v>1</v>
       </c>
       <c r="J195" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K195" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L195" t="b">
+        <v>0</v>
+      </c>
+      <c r="M195" t="b">
+        <v>0</v>
+      </c>
+      <c r="N195" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8566,12 +9740,18 @@
         <v>1</v>
       </c>
       <c r="J196" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K196" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L196" t="b">
+        <v>0</v>
+      </c>
+      <c r="M196" t="b">
+        <v>0</v>
+      </c>
+      <c r="N196" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8606,12 +9786,18 @@
         <v>1</v>
       </c>
       <c r="J197" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K197" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L197" t="b">
+        <v>0</v>
+      </c>
+      <c r="M197" t="b">
+        <v>0</v>
+      </c>
+      <c r="N197" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8646,12 +9832,18 @@
         <v>1</v>
       </c>
       <c r="J198" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K198" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L198" t="b">
+        <v>0</v>
+      </c>
+      <c r="M198" t="b">
+        <v>0</v>
+      </c>
+      <c r="N198" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8686,12 +9878,18 @@
         <v>1</v>
       </c>
       <c r="J199" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K199" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L199" t="b">
+        <v>0</v>
+      </c>
+      <c r="M199" t="b">
+        <v>0</v>
+      </c>
+      <c r="N199" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8726,12 +9924,18 @@
         <v>1</v>
       </c>
       <c r="J200" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K200" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L200" t="b">
+        <v>0</v>
+      </c>
+      <c r="M200" t="b">
+        <v>0</v>
+      </c>
+      <c r="N200" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8766,12 +9970,18 @@
         <v>1</v>
       </c>
       <c r="J201" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K201" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L201" t="b">
+        <v>0</v>
+      </c>
+      <c r="M201" t="b">
+        <v>0</v>
+      </c>
+      <c r="N201" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8806,12 +10016,18 @@
         <v>1</v>
       </c>
       <c r="J202" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K202" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L202" t="b">
+        <v>0</v>
+      </c>
+      <c r="M202" t="b">
+        <v>0</v>
+      </c>
+      <c r="N202" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8846,12 +10062,18 @@
         <v>1</v>
       </c>
       <c r="J203" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K203" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L203" t="b">
+        <v>0</v>
+      </c>
+      <c r="M203" t="b">
+        <v>0</v>
+      </c>
+      <c r="N203" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8886,12 +10108,18 @@
         <v>1</v>
       </c>
       <c r="J204" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K204" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L204" t="b">
+        <v>0</v>
+      </c>
+      <c r="M204" t="b">
+        <v>0</v>
+      </c>
+      <c r="N204" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8926,12 +10154,18 @@
         <v>1</v>
       </c>
       <c r="J205" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K205" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L205" t="b">
+        <v>0</v>
+      </c>
+      <c r="M205" t="b">
+        <v>0</v>
+      </c>
+      <c r="N205" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8969,9 +10203,15 @@
         <v>1</v>
       </c>
       <c r="K206" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L206" t="b">
+        <v>1</v>
+      </c>
+      <c r="M206" t="b">
+        <v>0</v>
+      </c>
+      <c r="N206" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9014,6 +10254,12 @@
       <c r="L207" t="b">
         <v>1</v>
       </c>
+      <c r="M207" t="b">
+        <v>1</v>
+      </c>
+      <c r="N207" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -9054,6 +10300,12 @@
       <c r="L208" t="b">
         <v>1</v>
       </c>
+      <c r="M208" t="b">
+        <v>1</v>
+      </c>
+      <c r="N208" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -9094,6 +10346,12 @@
       <c r="L209" t="b">
         <v>1</v>
       </c>
+      <c r="M209" t="b">
+        <v>1</v>
+      </c>
+      <c r="N209" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -9134,6 +10392,12 @@
       <c r="L210" t="b">
         <v>1</v>
       </c>
+      <c r="M210" t="b">
+        <v>1</v>
+      </c>
+      <c r="N210" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -9174,6 +10438,12 @@
       <c r="L211" t="b">
         <v>1</v>
       </c>
+      <c r="M211" t="b">
+        <v>1</v>
+      </c>
+      <c r="N211" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -9206,12 +10476,18 @@
         <v>0</v>
       </c>
       <c r="J212" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K212" t="b">
         <v>0</v>
       </c>
       <c r="L212" t="b">
+        <v>0</v>
+      </c>
+      <c r="M212" t="b">
+        <v>0</v>
+      </c>
+      <c r="N212" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9246,12 +10522,18 @@
         <v>0</v>
       </c>
       <c r="J213" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K213" t="b">
         <v>0</v>
       </c>
       <c r="L213" t="b">
+        <v>0</v>
+      </c>
+      <c r="M213" t="b">
+        <v>0</v>
+      </c>
+      <c r="N213" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9286,12 +10568,18 @@
         <v>0</v>
       </c>
       <c r="J214" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K214" t="b">
         <v>0</v>
       </c>
       <c r="L214" t="b">
+        <v>0</v>
+      </c>
+      <c r="M214" t="b">
+        <v>0</v>
+      </c>
+      <c r="N214" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9326,12 +10614,18 @@
         <v>0</v>
       </c>
       <c r="J215" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K215" t="b">
         <v>0</v>
       </c>
       <c r="L215" t="b">
+        <v>0</v>
+      </c>
+      <c r="M215" t="b">
+        <v>0</v>
+      </c>
+      <c r="N215" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9366,12 +10660,18 @@
         <v>0</v>
       </c>
       <c r="J216" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K216" t="b">
         <v>0</v>
       </c>
       <c r="L216" t="b">
+        <v>0</v>
+      </c>
+      <c r="M216" t="b">
+        <v>0</v>
+      </c>
+      <c r="N216" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9406,12 +10706,18 @@
         <v>0</v>
       </c>
       <c r="J217" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K217" t="b">
         <v>0</v>
       </c>
       <c r="L217" t="b">
+        <v>0</v>
+      </c>
+      <c r="M217" t="b">
+        <v>0</v>
+      </c>
+      <c r="N217" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9454,6 +10760,12 @@
       <c r="L218" t="b">
         <v>0</v>
       </c>
+      <c r="M218" t="b">
+        <v>0</v>
+      </c>
+      <c r="N218" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -9494,6 +10806,12 @@
       <c r="L219" t="b">
         <v>0</v>
       </c>
+      <c r="M219" t="b">
+        <v>0</v>
+      </c>
+      <c r="N219" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -9534,6 +10852,12 @@
       <c r="L220" t="b">
         <v>0</v>
       </c>
+      <c r="M220" t="b">
+        <v>0</v>
+      </c>
+      <c r="N220" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -9574,6 +10898,12 @@
       <c r="L221" t="b">
         <v>0</v>
       </c>
+      <c r="M221" t="b">
+        <v>0</v>
+      </c>
+      <c r="N221" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -9614,6 +10944,12 @@
       <c r="L222" t="b">
         <v>0</v>
       </c>
+      <c r="M222" t="b">
+        <v>0</v>
+      </c>
+      <c r="N222" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -9654,6 +10990,12 @@
       <c r="L223" t="b">
         <v>0</v>
       </c>
+      <c r="M223" t="b">
+        <v>0</v>
+      </c>
+      <c r="N223" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -9694,6 +11036,12 @@
       <c r="L224" t="b">
         <v>0</v>
       </c>
+      <c r="M224" t="b">
+        <v>0</v>
+      </c>
+      <c r="N224" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -9734,6 +11082,12 @@
       <c r="L225" t="b">
         <v>0</v>
       </c>
+      <c r="M225" t="b">
+        <v>0</v>
+      </c>
+      <c r="N225" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -9774,6 +11128,12 @@
       <c r="L226" t="b">
         <v>0</v>
       </c>
+      <c r="M226" t="b">
+        <v>0</v>
+      </c>
+      <c r="N226" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -9814,6 +11174,12 @@
       <c r="L227" t="b">
         <v>0</v>
       </c>
+      <c r="M227" t="b">
+        <v>0</v>
+      </c>
+      <c r="N227" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -9854,6 +11220,12 @@
       <c r="L228" t="b">
         <v>0</v>
       </c>
+      <c r="M228" t="b">
+        <v>0</v>
+      </c>
+      <c r="N228" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -9894,6 +11266,12 @@
       <c r="L229" t="b">
         <v>0</v>
       </c>
+      <c r="M229" t="b">
+        <v>0</v>
+      </c>
+      <c r="N229" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -9934,6 +11312,12 @@
       <c r="L230" t="b">
         <v>0</v>
       </c>
+      <c r="M230" t="b">
+        <v>0</v>
+      </c>
+      <c r="N230" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -9974,6 +11358,12 @@
       <c r="L231" t="b">
         <v>0</v>
       </c>
+      <c r="M231" t="b">
+        <v>0</v>
+      </c>
+      <c r="N231" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -10014,6 +11404,12 @@
       <c r="L232" t="b">
         <v>0</v>
       </c>
+      <c r="M232" t="b">
+        <v>0</v>
+      </c>
+      <c r="N232" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -10054,6 +11450,12 @@
       <c r="L233" t="b">
         <v>0</v>
       </c>
+      <c r="M233" t="b">
+        <v>0</v>
+      </c>
+      <c r="N233" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -10094,6 +11496,12 @@
       <c r="L234" t="b">
         <v>0</v>
       </c>
+      <c r="M234" t="b">
+        <v>0</v>
+      </c>
+      <c r="N234" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -10134,6 +11542,12 @@
       <c r="L235" t="b">
         <v>0</v>
       </c>
+      <c r="M235" t="b">
+        <v>0</v>
+      </c>
+      <c r="N235" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -10174,6 +11588,12 @@
       <c r="L236" t="b">
         <v>0</v>
       </c>
+      <c r="M236" t="b">
+        <v>0</v>
+      </c>
+      <c r="N236" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -10214,6 +11634,12 @@
       <c r="L237" t="b">
         <v>0</v>
       </c>
+      <c r="M237" t="b">
+        <v>0</v>
+      </c>
+      <c r="N237" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -10254,6 +11680,12 @@
       <c r="L238" t="b">
         <v>0</v>
       </c>
+      <c r="M238" t="b">
+        <v>0</v>
+      </c>
+      <c r="N238" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -10294,6 +11726,12 @@
       <c r="L239" t="b">
         <v>0</v>
       </c>
+      <c r="M239" t="b">
+        <v>0</v>
+      </c>
+      <c r="N239" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -10334,6 +11772,12 @@
       <c r="L240" t="b">
         <v>0</v>
       </c>
+      <c r="M240" t="b">
+        <v>0</v>
+      </c>
+      <c r="N240" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -10374,6 +11818,12 @@
       <c r="L241" t="b">
         <v>0</v>
       </c>
+      <c r="M241" t="b">
+        <v>0</v>
+      </c>
+      <c r="N241" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -10414,6 +11864,12 @@
       <c r="L242" t="b">
         <v>0</v>
       </c>
+      <c r="M242" t="b">
+        <v>0</v>
+      </c>
+      <c r="N242" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -10454,6 +11910,12 @@
       <c r="L243" t="b">
         <v>0</v>
       </c>
+      <c r="M243" t="b">
+        <v>0</v>
+      </c>
+      <c r="N243" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -10494,6 +11956,12 @@
       <c r="L244" t="b">
         <v>0</v>
       </c>
+      <c r="M244" t="b">
+        <v>0</v>
+      </c>
+      <c r="N244" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -10534,6 +12002,12 @@
       <c r="L245" t="b">
         <v>0</v>
       </c>
+      <c r="M245" t="b">
+        <v>0</v>
+      </c>
+      <c r="N245" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -10574,6 +12048,12 @@
       <c r="L246" t="b">
         <v>0</v>
       </c>
+      <c r="M246" t="b">
+        <v>0</v>
+      </c>
+      <c r="N246" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -10614,6 +12094,12 @@
       <c r="L247" t="b">
         <v>0</v>
       </c>
+      <c r="M247" t="b">
+        <v>0</v>
+      </c>
+      <c r="N247" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -10654,6 +12140,12 @@
       <c r="L248" t="b">
         <v>0</v>
       </c>
+      <c r="M248" t="b">
+        <v>0</v>
+      </c>
+      <c r="N248" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -10694,6 +12186,12 @@
       <c r="L249" t="b">
         <v>0</v>
       </c>
+      <c r="M249" t="b">
+        <v>0</v>
+      </c>
+      <c r="N249" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -10734,6 +12232,12 @@
       <c r="L250" t="b">
         <v>0</v>
       </c>
+      <c r="M250" t="b">
+        <v>0</v>
+      </c>
+      <c r="N250" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -10774,6 +12278,12 @@
       <c r="L251" t="b">
         <v>0</v>
       </c>
+      <c r="M251" t="b">
+        <v>0</v>
+      </c>
+      <c r="N251" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -10803,15 +12313,21 @@
         <v>0</v>
       </c>
       <c r="I252" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J252" t="b">
         <v>0</v>
       </c>
       <c r="K252" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L252" t="b">
+        <v>0</v>
+      </c>
+      <c r="M252" t="b">
+        <v>0</v>
+      </c>
+      <c r="N252" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10843,15 +12359,21 @@
         <v>0</v>
       </c>
       <c r="I253" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J253" t="b">
         <v>0</v>
       </c>
       <c r="K253" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L253" t="b">
+        <v>0</v>
+      </c>
+      <c r="M253" t="b">
+        <v>0</v>
+      </c>
+      <c r="N253" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10883,15 +12405,21 @@
         <v>0</v>
       </c>
       <c r="I254" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J254" t="b">
         <v>0</v>
       </c>
       <c r="K254" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L254" t="b">
+        <v>0</v>
+      </c>
+      <c r="M254" t="b">
+        <v>0</v>
+      </c>
+      <c r="N254" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10923,15 +12451,21 @@
         <v>0</v>
       </c>
       <c r="I255" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J255" t="b">
         <v>0</v>
       </c>
       <c r="K255" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L255" t="b">
+        <v>0</v>
+      </c>
+      <c r="M255" t="b">
+        <v>0</v>
+      </c>
+      <c r="N255" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10963,15 +12497,21 @@
         <v>0</v>
       </c>
       <c r="I256" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J256" t="b">
         <v>0</v>
       </c>
       <c r="K256" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L256" t="b">
+        <v>0</v>
+      </c>
+      <c r="M256" t="b">
+        <v>0</v>
+      </c>
+      <c r="N256" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11003,15 +12543,21 @@
         <v>0</v>
       </c>
       <c r="I257" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J257" t="b">
         <v>0</v>
       </c>
       <c r="K257" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L257" t="b">
+        <v>0</v>
+      </c>
+      <c r="M257" t="b">
+        <v>0</v>
+      </c>
+      <c r="N257" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11043,15 +12589,21 @@
         <v>0</v>
       </c>
       <c r="I258" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J258" t="b">
         <v>0</v>
       </c>
       <c r="K258" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L258" t="b">
+        <v>0</v>
+      </c>
+      <c r="M258" t="b">
+        <v>0</v>
+      </c>
+      <c r="N258" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11083,15 +12635,21 @@
         <v>0</v>
       </c>
       <c r="I259" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J259" t="b">
         <v>0</v>
       </c>
       <c r="K259" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L259" t="b">
+        <v>0</v>
+      </c>
+      <c r="M259" t="b">
+        <v>0</v>
+      </c>
+      <c r="N259" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11130,6 +12688,12 @@
         <v>0</v>
       </c>
       <c r="L260" t="b">
+        <v>0</v>
+      </c>
+      <c r="M260" t="b">
+        <v>0</v>
+      </c>
+      <c r="N260" t="b">
         <v>1</v>
       </c>
     </row>
@@ -11168,6 +12732,12 @@
         <v>0</v>
       </c>
       <c r="L261" t="b">
+        <v>0</v>
+      </c>
+      <c r="M261" t="b">
+        <v>0</v>
+      </c>
+      <c r="N261" t="b">
         <v>1</v>
       </c>
     </row>
@@ -11206,6 +12776,12 @@
         <v>0</v>
       </c>
       <c r="L262" t="b">
+        <v>0</v>
+      </c>
+      <c r="M262" t="b">
+        <v>0</v>
+      </c>
+      <c r="N262" t="b">
         <v>1</v>
       </c>
     </row>
@@ -11244,6 +12820,12 @@
         <v>0</v>
       </c>
       <c r="L263" t="b">
+        <v>0</v>
+      </c>
+      <c r="M263" t="b">
+        <v>0</v>
+      </c>
+      <c r="N263" t="b">
         <v>1</v>
       </c>
     </row>
@@ -11282,6 +12864,12 @@
         <v>0</v>
       </c>
       <c r="L264" t="b">
+        <v>0</v>
+      </c>
+      <c r="M264" t="b">
+        <v>0</v>
+      </c>
+      <c r="N264" t="b">
         <v>1</v>
       </c>
     </row>
@@ -11320,6 +12908,12 @@
         <v>0</v>
       </c>
       <c r="L265" t="b">
+        <v>0</v>
+      </c>
+      <c r="M265" t="b">
+        <v>0</v>
+      </c>
+      <c r="N265" t="b">
         <v>1</v>
       </c>
     </row>
@@ -11351,15 +12945,21 @@
         <v>0</v>
       </c>
       <c r="I266" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J266" t="b">
         <v>0</v>
       </c>
       <c r="K266" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L266" t="b">
+        <v>0</v>
+      </c>
+      <c r="M266" t="b">
+        <v>0</v>
+      </c>
+      <c r="N266" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11391,15 +12991,21 @@
         <v>0</v>
       </c>
       <c r="I267" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J267" t="b">
         <v>0</v>
       </c>
       <c r="K267" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L267" t="b">
+        <v>0</v>
+      </c>
+      <c r="M267" t="b">
+        <v>0</v>
+      </c>
+      <c r="N267" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11431,15 +13037,21 @@
         <v>0</v>
       </c>
       <c r="I268" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J268" t="b">
         <v>0</v>
       </c>
       <c r="K268" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L268" t="b">
+        <v>0</v>
+      </c>
+      <c r="M268" t="b">
+        <v>0</v>
+      </c>
+      <c r="N268" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11471,15 +13083,21 @@
         <v>0</v>
       </c>
       <c r="I269" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J269" t="b">
         <v>0</v>
       </c>
       <c r="K269" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L269" t="b">
+        <v>0</v>
+      </c>
+      <c r="M269" t="b">
+        <v>0</v>
+      </c>
+      <c r="N269" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11511,15 +13129,21 @@
         <v>0</v>
       </c>
       <c r="I270" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J270" t="b">
         <v>0</v>
       </c>
       <c r="K270" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L270" t="b">
+        <v>0</v>
+      </c>
+      <c r="M270" t="b">
+        <v>0</v>
+      </c>
+      <c r="N270" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11551,15 +13175,21 @@
         <v>0</v>
       </c>
       <c r="I271" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J271" t="b">
         <v>0</v>
       </c>
       <c r="K271" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L271" t="b">
+        <v>0</v>
+      </c>
+      <c r="M271" t="b">
+        <v>0</v>
+      </c>
+      <c r="N271" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11591,15 +13221,21 @@
         <v>1</v>
       </c>
       <c r="I272" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J272" t="b">
         <v>1</v>
       </c>
       <c r="K272" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L272" t="b">
+        <v>1</v>
+      </c>
+      <c r="M272" t="b">
+        <v>0</v>
+      </c>
+      <c r="N272" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11631,15 +13267,21 @@
         <v>1</v>
       </c>
       <c r="I273" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J273" t="b">
         <v>1</v>
       </c>
       <c r="K273" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L273" t="b">
+        <v>1</v>
+      </c>
+      <c r="M273" t="b">
+        <v>0</v>
+      </c>
+      <c r="N273" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11671,15 +13313,21 @@
         <v>1</v>
       </c>
       <c r="I274" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J274" t="b">
         <v>1</v>
       </c>
       <c r="K274" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L274" t="b">
+        <v>1</v>
+      </c>
+      <c r="M274" t="b">
+        <v>0</v>
+      </c>
+      <c r="N274" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11711,15 +13359,21 @@
         <v>1</v>
       </c>
       <c r="I275" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J275" t="b">
         <v>1</v>
       </c>
       <c r="K275" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L275" t="b">
+        <v>1</v>
+      </c>
+      <c r="M275" t="b">
+        <v>0</v>
+      </c>
+      <c r="N275" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11751,15 +13405,21 @@
         <v>1</v>
       </c>
       <c r="I276" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J276" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K276" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L276" t="b">
+        <v>1</v>
+      </c>
+      <c r="M276" t="b">
+        <v>0</v>
+      </c>
+      <c r="N276" t="b">
         <v>1</v>
       </c>
     </row>
@@ -11791,15 +13451,21 @@
         <v>1</v>
       </c>
       <c r="I277" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J277" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K277" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L277" t="b">
+        <v>1</v>
+      </c>
+      <c r="M277" t="b">
+        <v>0</v>
+      </c>
+      <c r="N277" t="b">
         <v>1</v>
       </c>
     </row>
@@ -11831,15 +13497,21 @@
         <v>1</v>
       </c>
       <c r="I278" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J278" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K278" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L278" t="b">
+        <v>1</v>
+      </c>
+      <c r="M278" t="b">
+        <v>0</v>
+      </c>
+      <c r="N278" t="b">
         <v>1</v>
       </c>
     </row>
@@ -11871,15 +13543,21 @@
         <v>1</v>
       </c>
       <c r="I279" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J279" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K279" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L279" t="b">
+        <v>1</v>
+      </c>
+      <c r="M279" t="b">
+        <v>0</v>
+      </c>
+      <c r="N279" t="b">
         <v>1</v>
       </c>
     </row>
@@ -11911,15 +13589,21 @@
         <v>1</v>
       </c>
       <c r="I280" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J280" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K280" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L280" t="b">
+        <v>1</v>
+      </c>
+      <c r="M280" t="b">
+        <v>0</v>
+      </c>
+      <c r="N280" t="b">
         <v>1</v>
       </c>
     </row>
@@ -11951,15 +13635,21 @@
         <v>1</v>
       </c>
       <c r="I281" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J281" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K281" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L281" t="b">
+        <v>1</v>
+      </c>
+      <c r="M281" t="b">
+        <v>0</v>
+      </c>
+      <c r="N281" t="b">
         <v>1</v>
       </c>
     </row>
@@ -11997,9 +13687,15 @@
         <v>1</v>
       </c>
       <c r="K282" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L282" t="b">
+        <v>1</v>
+      </c>
+      <c r="M282" t="b">
+        <v>0</v>
+      </c>
+      <c r="N282" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12037,9 +13733,15 @@
         <v>1</v>
       </c>
       <c r="K283" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L283" t="b">
+        <v>1</v>
+      </c>
+      <c r="M283" t="b">
+        <v>0</v>
+      </c>
+      <c r="N283" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12077,9 +13779,15 @@
         <v>1</v>
       </c>
       <c r="K284" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L284" t="b">
+        <v>1</v>
+      </c>
+      <c r="M284" t="b">
+        <v>0</v>
+      </c>
+      <c r="N284" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12117,9 +13825,15 @@
         <v>1</v>
       </c>
       <c r="K285" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L285" t="b">
+        <v>1</v>
+      </c>
+      <c r="M285" t="b">
+        <v>0</v>
+      </c>
+      <c r="N285" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Project 1 Data Quality Assessment/D2 Temporal Continuity & Information Availability/artifacts/data/D2_process_floor_casebook.xlsx
+++ b/Project 1 Data Quality Assessment/D2 Temporal Continuity & Information Availability/artifacts/data/D2_process_floor_casebook.xlsx
@@ -13928,7 +13928,7 @@
         <v>0.9312203888253554</v>
       </c>
       <c r="I2" t="n">
-        <v>4.977722412822887</v>
+        <v>4.978304803741824</v>
       </c>
     </row>
     <row r="3">
@@ -13961,7 +13961,7 @@
         <v>1.241627185100474</v>
       </c>
       <c r="I3" t="n">
-        <v>4.965077722715364</v>
+        <v>4.966942886359648</v>
       </c>
     </row>
   </sheetData>

--- a/Project 1 Data Quality Assessment/D2 Temporal Continuity & Information Availability/artifacts/data/D2_process_floor_casebook.xlsx
+++ b/Project 1 Data Quality Assessment/D2 Temporal Continuity & Information Availability/artifacts/data/D2_process_floor_casebook.xlsx
@@ -696,7 +696,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>35.29411764705883</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -710,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N285"/>
+  <dimension ref="A1:Q285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,6 +781,21 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>hard_availability_loss</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>continuity_unavailable</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>any_information_unavailable</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>qfa_unavailable</t>
         </is>
       </c>
@@ -830,6 +845,15 @@
       <c r="N2" t="b">
         <v>0</v>
       </c>
+      <c r="O2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -876,6 +900,15 @@
       <c r="N3" t="b">
         <v>0</v>
       </c>
+      <c r="O3" t="b">
+        <v>0</v>
+      </c>
+      <c r="P3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -922,6 +955,15 @@
       <c r="N4" t="b">
         <v>0</v>
       </c>
+      <c r="O4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -968,6 +1010,15 @@
       <c r="N5" t="b">
         <v>0</v>
       </c>
+      <c r="O5" t="b">
+        <v>0</v>
+      </c>
+      <c r="P5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1014,6 +1065,15 @@
       <c r="N6" t="b">
         <v>0</v>
       </c>
+      <c r="O6" t="b">
+        <v>0</v>
+      </c>
+      <c r="P6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1060,6 +1120,15 @@
       <c r="N7" t="b">
         <v>0</v>
       </c>
+      <c r="O7" t="b">
+        <v>0</v>
+      </c>
+      <c r="P7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1106,6 +1175,15 @@
       <c r="N8" t="b">
         <v>0</v>
       </c>
+      <c r="O8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1152,6 +1230,15 @@
       <c r="N9" t="b">
         <v>0</v>
       </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1198,6 +1285,15 @@
       <c r="N10" t="b">
         <v>0</v>
       </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1244,6 +1340,15 @@
       <c r="N11" t="b">
         <v>0</v>
       </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1290,6 +1395,15 @@
       <c r="N12" t="b">
         <v>0</v>
       </c>
+      <c r="O12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1336,6 +1450,15 @@
       <c r="N13" t="b">
         <v>0</v>
       </c>
+      <c r="O13" t="b">
+        <v>0</v>
+      </c>
+      <c r="P13" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1382,6 +1505,15 @@
       <c r="N14" t="b">
         <v>0</v>
       </c>
+      <c r="O14" t="b">
+        <v>0</v>
+      </c>
+      <c r="P14" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1428,6 +1560,15 @@
       <c r="N15" t="b">
         <v>0</v>
       </c>
+      <c r="O15" t="b">
+        <v>0</v>
+      </c>
+      <c r="P15" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1474,6 +1615,15 @@
       <c r="N16" t="b">
         <v>0</v>
       </c>
+      <c r="O16" t="b">
+        <v>0</v>
+      </c>
+      <c r="P16" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1520,6 +1670,15 @@
       <c r="N17" t="b">
         <v>0</v>
       </c>
+      <c r="O17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P17" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1566,6 +1725,15 @@
       <c r="N18" t="b">
         <v>0</v>
       </c>
+      <c r="O18" t="b">
+        <v>0</v>
+      </c>
+      <c r="P18" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1612,6 +1780,15 @@
       <c r="N19" t="b">
         <v>0</v>
       </c>
+      <c r="O19" t="b">
+        <v>0</v>
+      </c>
+      <c r="P19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1658,6 +1835,15 @@
       <c r="N20" t="b">
         <v>0</v>
       </c>
+      <c r="O20" t="b">
+        <v>0</v>
+      </c>
+      <c r="P20" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1704,6 +1890,15 @@
       <c r="N21" t="b">
         <v>0</v>
       </c>
+      <c r="O21" t="b">
+        <v>0</v>
+      </c>
+      <c r="P21" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1750,6 +1945,15 @@
       <c r="N22" t="b">
         <v>0</v>
       </c>
+      <c r="O22" t="b">
+        <v>0</v>
+      </c>
+      <c r="P22" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1796,6 +2000,15 @@
       <c r="N23" t="b">
         <v>0</v>
       </c>
+      <c r="O23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1842,6 +2055,15 @@
       <c r="N24" t="b">
         <v>0</v>
       </c>
+      <c r="O24" t="b">
+        <v>0</v>
+      </c>
+      <c r="P24" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1888,6 +2110,15 @@
       <c r="N25" t="b">
         <v>0</v>
       </c>
+      <c r="O25" t="b">
+        <v>0</v>
+      </c>
+      <c r="P25" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1934,6 +2165,15 @@
       <c r="N26" t="b">
         <v>0</v>
       </c>
+      <c r="O26" t="b">
+        <v>0</v>
+      </c>
+      <c r="P26" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1980,6 +2220,15 @@
       <c r="N27" t="b">
         <v>0</v>
       </c>
+      <c r="O27" t="b">
+        <v>0</v>
+      </c>
+      <c r="P27" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2026,6 +2275,15 @@
       <c r="N28" t="b">
         <v>0</v>
       </c>
+      <c r="O28" t="b">
+        <v>0</v>
+      </c>
+      <c r="P28" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2072,6 +2330,15 @@
       <c r="N29" t="b">
         <v>0</v>
       </c>
+      <c r="O29" t="b">
+        <v>0</v>
+      </c>
+      <c r="P29" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2118,6 +2385,15 @@
       <c r="N30" t="b">
         <v>0</v>
       </c>
+      <c r="O30" t="b">
+        <v>0</v>
+      </c>
+      <c r="P30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2164,6 +2440,15 @@
       <c r="N31" t="b">
         <v>0</v>
       </c>
+      <c r="O31" t="b">
+        <v>0</v>
+      </c>
+      <c r="P31" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2210,6 +2495,15 @@
       <c r="N32" t="b">
         <v>0</v>
       </c>
+      <c r="O32" t="b">
+        <v>0</v>
+      </c>
+      <c r="P32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2256,6 +2550,15 @@
       <c r="N33" t="b">
         <v>0</v>
       </c>
+      <c r="O33" t="b">
+        <v>0</v>
+      </c>
+      <c r="P33" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2302,6 +2605,15 @@
       <c r="N34" t="b">
         <v>0</v>
       </c>
+      <c r="O34" t="b">
+        <v>0</v>
+      </c>
+      <c r="P34" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2348,6 +2660,15 @@
       <c r="N35" t="b">
         <v>0</v>
       </c>
+      <c r="O35" t="b">
+        <v>0</v>
+      </c>
+      <c r="P35" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2394,6 +2715,15 @@
       <c r="N36" t="b">
         <v>0</v>
       </c>
+      <c r="O36" t="b">
+        <v>0</v>
+      </c>
+      <c r="P36" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2440,6 +2770,15 @@
       <c r="N37" t="b">
         <v>0</v>
       </c>
+      <c r="O37" t="b">
+        <v>0</v>
+      </c>
+      <c r="P37" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2486,6 +2825,15 @@
       <c r="N38" t="b">
         <v>0</v>
       </c>
+      <c r="O38" t="b">
+        <v>0</v>
+      </c>
+      <c r="P38" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2532,6 +2880,15 @@
       <c r="N39" t="b">
         <v>0</v>
       </c>
+      <c r="O39" t="b">
+        <v>0</v>
+      </c>
+      <c r="P39" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2578,6 +2935,15 @@
       <c r="N40" t="b">
         <v>0</v>
       </c>
+      <c r="O40" t="b">
+        <v>0</v>
+      </c>
+      <c r="P40" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2624,6 +2990,15 @@
       <c r="N41" t="b">
         <v>0</v>
       </c>
+      <c r="O41" t="b">
+        <v>0</v>
+      </c>
+      <c r="P41" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2670,6 +3045,15 @@
       <c r="N42" t="b">
         <v>0</v>
       </c>
+      <c r="O42" t="b">
+        <v>0</v>
+      </c>
+      <c r="P42" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2716,6 +3100,15 @@
       <c r="N43" t="b">
         <v>0</v>
       </c>
+      <c r="O43" t="b">
+        <v>0</v>
+      </c>
+      <c r="P43" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2762,6 +3155,15 @@
       <c r="N44" t="b">
         <v>0</v>
       </c>
+      <c r="O44" t="b">
+        <v>0</v>
+      </c>
+      <c r="P44" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2808,6 +3210,15 @@
       <c r="N45" t="b">
         <v>0</v>
       </c>
+      <c r="O45" t="b">
+        <v>0</v>
+      </c>
+      <c r="P45" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2854,6 +3265,15 @@
       <c r="N46" t="b">
         <v>0</v>
       </c>
+      <c r="O46" t="b">
+        <v>0</v>
+      </c>
+      <c r="P46" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2900,6 +3320,15 @@
       <c r="N47" t="b">
         <v>0</v>
       </c>
+      <c r="O47" t="b">
+        <v>0</v>
+      </c>
+      <c r="P47" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2946,6 +3375,15 @@
       <c r="N48" t="b">
         <v>0</v>
       </c>
+      <c r="O48" t="b">
+        <v>0</v>
+      </c>
+      <c r="P48" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2992,6 +3430,15 @@
       <c r="N49" t="b">
         <v>0</v>
       </c>
+      <c r="O49" t="b">
+        <v>0</v>
+      </c>
+      <c r="P49" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3038,6 +3485,15 @@
       <c r="N50" t="b">
         <v>0</v>
       </c>
+      <c r="O50" t="b">
+        <v>0</v>
+      </c>
+      <c r="P50" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3084,6 +3540,15 @@
       <c r="N51" t="b">
         <v>0</v>
       </c>
+      <c r="O51" t="b">
+        <v>0</v>
+      </c>
+      <c r="P51" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3130,6 +3595,15 @@
       <c r="N52" t="b">
         <v>0</v>
       </c>
+      <c r="O52" t="b">
+        <v>0</v>
+      </c>
+      <c r="P52" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3176,6 +3650,15 @@
       <c r="N53" t="b">
         <v>0</v>
       </c>
+      <c r="O53" t="b">
+        <v>0</v>
+      </c>
+      <c r="P53" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3222,6 +3705,15 @@
       <c r="N54" t="b">
         <v>0</v>
       </c>
+      <c r="O54" t="b">
+        <v>0</v>
+      </c>
+      <c r="P54" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3268,6 +3760,15 @@
       <c r="N55" t="b">
         <v>0</v>
       </c>
+      <c r="O55" t="b">
+        <v>0</v>
+      </c>
+      <c r="P55" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3314,6 +3815,15 @@
       <c r="N56" t="b">
         <v>0</v>
       </c>
+      <c r="O56" t="b">
+        <v>0</v>
+      </c>
+      <c r="P56" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3360,6 +3870,15 @@
       <c r="N57" t="b">
         <v>0</v>
       </c>
+      <c r="O57" t="b">
+        <v>0</v>
+      </c>
+      <c r="P57" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3406,6 +3925,15 @@
       <c r="N58" t="b">
         <v>0</v>
       </c>
+      <c r="O58" t="b">
+        <v>0</v>
+      </c>
+      <c r="P58" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3452,6 +3980,15 @@
       <c r="N59" t="b">
         <v>0</v>
       </c>
+      <c r="O59" t="b">
+        <v>0</v>
+      </c>
+      <c r="P59" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3498,6 +4035,15 @@
       <c r="N60" t="b">
         <v>0</v>
       </c>
+      <c r="O60" t="b">
+        <v>0</v>
+      </c>
+      <c r="P60" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3544,6 +4090,15 @@
       <c r="N61" t="b">
         <v>0</v>
       </c>
+      <c r="O61" t="b">
+        <v>0</v>
+      </c>
+      <c r="P61" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3590,6 +4145,15 @@
       <c r="N62" t="b">
         <v>0</v>
       </c>
+      <c r="O62" t="b">
+        <v>0</v>
+      </c>
+      <c r="P62" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3636,6 +4200,15 @@
       <c r="N63" t="b">
         <v>0</v>
       </c>
+      <c r="O63" t="b">
+        <v>0</v>
+      </c>
+      <c r="P63" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3682,6 +4255,15 @@
       <c r="N64" t="b">
         <v>0</v>
       </c>
+      <c r="O64" t="b">
+        <v>0</v>
+      </c>
+      <c r="P64" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3728,6 +4310,15 @@
       <c r="N65" t="b">
         <v>0</v>
       </c>
+      <c r="O65" t="b">
+        <v>0</v>
+      </c>
+      <c r="P65" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3774,6 +4365,15 @@
       <c r="N66" t="b">
         <v>0</v>
       </c>
+      <c r="O66" t="b">
+        <v>0</v>
+      </c>
+      <c r="P66" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3820,6 +4420,15 @@
       <c r="N67" t="b">
         <v>0</v>
       </c>
+      <c r="O67" t="b">
+        <v>0</v>
+      </c>
+      <c r="P67" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q67" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3866,6 +4475,15 @@
       <c r="N68" t="b">
         <v>0</v>
       </c>
+      <c r="O68" t="b">
+        <v>0</v>
+      </c>
+      <c r="P68" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q68" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3912,6 +4530,15 @@
       <c r="N69" t="b">
         <v>0</v>
       </c>
+      <c r="O69" t="b">
+        <v>0</v>
+      </c>
+      <c r="P69" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3958,6 +4585,15 @@
       <c r="N70" t="b">
         <v>0</v>
       </c>
+      <c r="O70" t="b">
+        <v>0</v>
+      </c>
+      <c r="P70" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q70" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4004,6 +4640,15 @@
       <c r="N71" t="b">
         <v>0</v>
       </c>
+      <c r="O71" t="b">
+        <v>0</v>
+      </c>
+      <c r="P71" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q71" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4050,6 +4695,15 @@
       <c r="N72" t="b">
         <v>0</v>
       </c>
+      <c r="O72" t="b">
+        <v>0</v>
+      </c>
+      <c r="P72" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q72" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4096,6 +4750,15 @@
       <c r="N73" t="b">
         <v>0</v>
       </c>
+      <c r="O73" t="b">
+        <v>0</v>
+      </c>
+      <c r="P73" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4142,6 +4805,15 @@
       <c r="N74" t="b">
         <v>0</v>
       </c>
+      <c r="O74" t="b">
+        <v>0</v>
+      </c>
+      <c r="P74" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q74" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4188,6 +4860,15 @@
       <c r="N75" t="b">
         <v>0</v>
       </c>
+      <c r="O75" t="b">
+        <v>0</v>
+      </c>
+      <c r="P75" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4234,6 +4915,15 @@
       <c r="N76" t="b">
         <v>0</v>
       </c>
+      <c r="O76" t="b">
+        <v>0</v>
+      </c>
+      <c r="P76" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4280,6 +4970,15 @@
       <c r="N77" t="b">
         <v>0</v>
       </c>
+      <c r="O77" t="b">
+        <v>0</v>
+      </c>
+      <c r="P77" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q77" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4326,6 +5025,15 @@
       <c r="N78" t="b">
         <v>0</v>
       </c>
+      <c r="O78" t="b">
+        <v>0</v>
+      </c>
+      <c r="P78" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q78" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4372,6 +5080,15 @@
       <c r="N79" t="b">
         <v>0</v>
       </c>
+      <c r="O79" t="b">
+        <v>0</v>
+      </c>
+      <c r="P79" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4418,6 +5135,15 @@
       <c r="N80" t="b">
         <v>0</v>
       </c>
+      <c r="O80" t="b">
+        <v>0</v>
+      </c>
+      <c r="P80" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q80" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4464,6 +5190,15 @@
       <c r="N81" t="b">
         <v>0</v>
       </c>
+      <c r="O81" t="b">
+        <v>0</v>
+      </c>
+      <c r="P81" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4510,6 +5245,15 @@
       <c r="N82" t="b">
         <v>0</v>
       </c>
+      <c r="O82" t="b">
+        <v>0</v>
+      </c>
+      <c r="P82" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4556,6 +5300,15 @@
       <c r="N83" t="b">
         <v>0</v>
       </c>
+      <c r="O83" t="b">
+        <v>0</v>
+      </c>
+      <c r="P83" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q83" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4602,6 +5355,15 @@
       <c r="N84" t="b">
         <v>0</v>
       </c>
+      <c r="O84" t="b">
+        <v>0</v>
+      </c>
+      <c r="P84" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q84" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4648,6 +5410,15 @@
       <c r="N85" t="b">
         <v>0</v>
       </c>
+      <c r="O85" t="b">
+        <v>0</v>
+      </c>
+      <c r="P85" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q85" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4694,6 +5465,15 @@
       <c r="N86" t="b">
         <v>0</v>
       </c>
+      <c r="O86" t="b">
+        <v>0</v>
+      </c>
+      <c r="P86" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q86" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4740,6 +5520,15 @@
       <c r="N87" t="b">
         <v>0</v>
       </c>
+      <c r="O87" t="b">
+        <v>0</v>
+      </c>
+      <c r="P87" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q87" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4786,6 +5575,15 @@
       <c r="N88" t="b">
         <v>0</v>
       </c>
+      <c r="O88" t="b">
+        <v>0</v>
+      </c>
+      <c r="P88" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q88" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4832,6 +5630,15 @@
       <c r="N89" t="b">
         <v>0</v>
       </c>
+      <c r="O89" t="b">
+        <v>0</v>
+      </c>
+      <c r="P89" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q89" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4878,6 +5685,15 @@
       <c r="N90" t="b">
         <v>0</v>
       </c>
+      <c r="O90" t="b">
+        <v>0</v>
+      </c>
+      <c r="P90" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4924,6 +5740,15 @@
       <c r="N91" t="b">
         <v>0</v>
       </c>
+      <c r="O91" t="b">
+        <v>0</v>
+      </c>
+      <c r="P91" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q91" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4970,6 +5795,15 @@
       <c r="N92" t="b">
         <v>0</v>
       </c>
+      <c r="O92" t="b">
+        <v>0</v>
+      </c>
+      <c r="P92" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q92" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5016,6 +5850,15 @@
       <c r="N93" t="b">
         <v>0</v>
       </c>
+      <c r="O93" t="b">
+        <v>0</v>
+      </c>
+      <c r="P93" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q93" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5062,6 +5905,15 @@
       <c r="N94" t="b">
         <v>0</v>
       </c>
+      <c r="O94" t="b">
+        <v>0</v>
+      </c>
+      <c r="P94" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q94" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5108,6 +5960,15 @@
       <c r="N95" t="b">
         <v>0</v>
       </c>
+      <c r="O95" t="b">
+        <v>0</v>
+      </c>
+      <c r="P95" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q95" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5154,6 +6015,15 @@
       <c r="N96" t="b">
         <v>0</v>
       </c>
+      <c r="O96" t="b">
+        <v>0</v>
+      </c>
+      <c r="P96" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q96" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5200,6 +6070,15 @@
       <c r="N97" t="b">
         <v>1</v>
       </c>
+      <c r="O97" t="b">
+        <v>0</v>
+      </c>
+      <c r="P97" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q97" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5246,6 +6125,15 @@
       <c r="N98" t="b">
         <v>1</v>
       </c>
+      <c r="O98" t="b">
+        <v>0</v>
+      </c>
+      <c r="P98" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q98" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5292,6 +6180,15 @@
       <c r="N99" t="b">
         <v>1</v>
       </c>
+      <c r="O99" t="b">
+        <v>0</v>
+      </c>
+      <c r="P99" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q99" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5338,6 +6235,15 @@
       <c r="N100" t="b">
         <v>1</v>
       </c>
+      <c r="O100" t="b">
+        <v>0</v>
+      </c>
+      <c r="P100" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q100" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5384,6 +6290,15 @@
       <c r="N101" t="b">
         <v>1</v>
       </c>
+      <c r="O101" t="b">
+        <v>0</v>
+      </c>
+      <c r="P101" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q101" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5430,6 +6345,15 @@
       <c r="N102" t="b">
         <v>1</v>
       </c>
+      <c r="O102" t="b">
+        <v>0</v>
+      </c>
+      <c r="P102" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q102" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5476,6 +6400,15 @@
       <c r="N103" t="b">
         <v>1</v>
       </c>
+      <c r="O103" t="b">
+        <v>0</v>
+      </c>
+      <c r="P103" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q103" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5522,6 +6455,15 @@
       <c r="N104" t="b">
         <v>1</v>
       </c>
+      <c r="O104" t="b">
+        <v>0</v>
+      </c>
+      <c r="P104" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q104" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5568,6 +6510,15 @@
       <c r="N105" t="b">
         <v>1</v>
       </c>
+      <c r="O105" t="b">
+        <v>0</v>
+      </c>
+      <c r="P105" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q105" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5614,6 +6565,15 @@
       <c r="N106" t="b">
         <v>1</v>
       </c>
+      <c r="O106" t="b">
+        <v>0</v>
+      </c>
+      <c r="P106" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q106" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5660,6 +6620,15 @@
       <c r="N107" t="b">
         <v>1</v>
       </c>
+      <c r="O107" t="b">
+        <v>0</v>
+      </c>
+      <c r="P107" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q107" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5706,6 +6675,15 @@
       <c r="N108" t="b">
         <v>1</v>
       </c>
+      <c r="O108" t="b">
+        <v>0</v>
+      </c>
+      <c r="P108" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q108" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5752,6 +6730,15 @@
       <c r="N109" t="b">
         <v>1</v>
       </c>
+      <c r="O109" t="b">
+        <v>0</v>
+      </c>
+      <c r="P109" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q109" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5798,6 +6785,15 @@
       <c r="N110" t="b">
         <v>1</v>
       </c>
+      <c r="O110" t="b">
+        <v>0</v>
+      </c>
+      <c r="P110" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q110" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5844,6 +6840,15 @@
       <c r="N111" t="b">
         <v>1</v>
       </c>
+      <c r="O111" t="b">
+        <v>0</v>
+      </c>
+      <c r="P111" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q111" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5890,6 +6895,15 @@
       <c r="N112" t="b">
         <v>0</v>
       </c>
+      <c r="O112" t="b">
+        <v>0</v>
+      </c>
+      <c r="P112" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q112" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5936,6 +6950,15 @@
       <c r="N113" t="b">
         <v>0</v>
       </c>
+      <c r="O113" t="b">
+        <v>0</v>
+      </c>
+      <c r="P113" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q113" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5982,6 +7005,15 @@
       <c r="N114" t="b">
         <v>0</v>
       </c>
+      <c r="O114" t="b">
+        <v>0</v>
+      </c>
+      <c r="P114" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q114" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6028,6 +7060,15 @@
       <c r="N115" t="b">
         <v>0</v>
       </c>
+      <c r="O115" t="b">
+        <v>0</v>
+      </c>
+      <c r="P115" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q115" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6074,6 +7115,15 @@
       <c r="N116" t="b">
         <v>0</v>
       </c>
+      <c r="O116" t="b">
+        <v>0</v>
+      </c>
+      <c r="P116" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q116" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6120,6 +7170,15 @@
       <c r="N117" t="b">
         <v>0</v>
       </c>
+      <c r="O117" t="b">
+        <v>0</v>
+      </c>
+      <c r="P117" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q117" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -6166,6 +7225,15 @@
       <c r="N118" t="b">
         <v>0</v>
       </c>
+      <c r="O118" t="b">
+        <v>0</v>
+      </c>
+      <c r="P118" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q118" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6212,6 +7280,15 @@
       <c r="N119" t="b">
         <v>0</v>
       </c>
+      <c r="O119" t="b">
+        <v>0</v>
+      </c>
+      <c r="P119" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q119" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -6258,6 +7335,15 @@
       <c r="N120" t="b">
         <v>0</v>
       </c>
+      <c r="O120" t="b">
+        <v>0</v>
+      </c>
+      <c r="P120" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q120" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6304,6 +7390,15 @@
       <c r="N121" t="b">
         <v>0</v>
       </c>
+      <c r="O121" t="b">
+        <v>0</v>
+      </c>
+      <c r="P121" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q121" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6350,6 +7445,15 @@
       <c r="N122" t="b">
         <v>0</v>
       </c>
+      <c r="O122" t="b">
+        <v>0</v>
+      </c>
+      <c r="P122" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q122" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -6396,6 +7500,15 @@
       <c r="N123" t="b">
         <v>0</v>
       </c>
+      <c r="O123" t="b">
+        <v>0</v>
+      </c>
+      <c r="P123" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q123" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -6442,6 +7555,15 @@
       <c r="N124" t="b">
         <v>0</v>
       </c>
+      <c r="O124" t="b">
+        <v>0</v>
+      </c>
+      <c r="P124" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q124" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -6488,6 +7610,15 @@
       <c r="N125" t="b">
         <v>0</v>
       </c>
+      <c r="O125" t="b">
+        <v>0</v>
+      </c>
+      <c r="P125" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q125" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -6534,6 +7665,15 @@
       <c r="N126" t="b">
         <v>0</v>
       </c>
+      <c r="O126" t="b">
+        <v>0</v>
+      </c>
+      <c r="P126" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q126" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -6580,6 +7720,15 @@
       <c r="N127" t="b">
         <v>0</v>
       </c>
+      <c r="O127" t="b">
+        <v>0</v>
+      </c>
+      <c r="P127" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q127" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -6626,6 +7775,15 @@
       <c r="N128" t="b">
         <v>0</v>
       </c>
+      <c r="O128" t="b">
+        <v>0</v>
+      </c>
+      <c r="P128" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q128" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -6672,6 +7830,15 @@
       <c r="N129" t="b">
         <v>0</v>
       </c>
+      <c r="O129" t="b">
+        <v>0</v>
+      </c>
+      <c r="P129" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q129" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -6718,6 +7885,15 @@
       <c r="N130" t="b">
         <v>0</v>
       </c>
+      <c r="O130" t="b">
+        <v>0</v>
+      </c>
+      <c r="P130" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q130" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -6764,6 +7940,15 @@
       <c r="N131" t="b">
         <v>0</v>
       </c>
+      <c r="O131" t="b">
+        <v>0</v>
+      </c>
+      <c r="P131" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q131" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -6810,6 +7995,15 @@
       <c r="N132" t="b">
         <v>0</v>
       </c>
+      <c r="O132" t="b">
+        <v>0</v>
+      </c>
+      <c r="P132" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q132" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -6856,6 +8050,15 @@
       <c r="N133" t="b">
         <v>0</v>
       </c>
+      <c r="O133" t="b">
+        <v>0</v>
+      </c>
+      <c r="P133" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q133" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -6902,6 +8105,15 @@
       <c r="N134" t="b">
         <v>0</v>
       </c>
+      <c r="O134" t="b">
+        <v>0</v>
+      </c>
+      <c r="P134" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q134" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -6948,6 +8160,15 @@
       <c r="N135" t="b">
         <v>0</v>
       </c>
+      <c r="O135" t="b">
+        <v>0</v>
+      </c>
+      <c r="P135" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q135" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -6994,6 +8215,15 @@
       <c r="N136" t="b">
         <v>0</v>
       </c>
+      <c r="O136" t="b">
+        <v>0</v>
+      </c>
+      <c r="P136" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q136" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -7040,6 +8270,15 @@
       <c r="N137" t="b">
         <v>0</v>
       </c>
+      <c r="O137" t="b">
+        <v>0</v>
+      </c>
+      <c r="P137" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q137" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -7086,6 +8325,15 @@
       <c r="N138" t="b">
         <v>0</v>
       </c>
+      <c r="O138" t="b">
+        <v>0</v>
+      </c>
+      <c r="P138" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q138" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -7132,6 +8380,15 @@
       <c r="N139" t="b">
         <v>0</v>
       </c>
+      <c r="O139" t="b">
+        <v>0</v>
+      </c>
+      <c r="P139" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q139" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -7178,6 +8435,15 @@
       <c r="N140" t="b">
         <v>0</v>
       </c>
+      <c r="O140" t="b">
+        <v>0</v>
+      </c>
+      <c r="P140" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q140" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -7224,6 +8490,15 @@
       <c r="N141" t="b">
         <v>0</v>
       </c>
+      <c r="O141" t="b">
+        <v>0</v>
+      </c>
+      <c r="P141" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q141" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -7270,6 +8545,15 @@
       <c r="N142" t="b">
         <v>0</v>
       </c>
+      <c r="O142" t="b">
+        <v>0</v>
+      </c>
+      <c r="P142" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q142" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -7316,6 +8600,15 @@
       <c r="N143" t="b">
         <v>0</v>
       </c>
+      <c r="O143" t="b">
+        <v>0</v>
+      </c>
+      <c r="P143" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q143" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -7362,6 +8655,15 @@
       <c r="N144" t="b">
         <v>0</v>
       </c>
+      <c r="O144" t="b">
+        <v>0</v>
+      </c>
+      <c r="P144" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q144" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -7408,6 +8710,15 @@
       <c r="N145" t="b">
         <v>0</v>
       </c>
+      <c r="O145" t="b">
+        <v>0</v>
+      </c>
+      <c r="P145" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q145" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -7454,6 +8765,15 @@
       <c r="N146" t="b">
         <v>0</v>
       </c>
+      <c r="O146" t="b">
+        <v>0</v>
+      </c>
+      <c r="P146" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q146" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -7500,6 +8820,15 @@
       <c r="N147" t="b">
         <v>0</v>
       </c>
+      <c r="O147" t="b">
+        <v>0</v>
+      </c>
+      <c r="P147" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q147" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -7546,6 +8875,15 @@
       <c r="N148" t="b">
         <v>0</v>
       </c>
+      <c r="O148" t="b">
+        <v>0</v>
+      </c>
+      <c r="P148" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q148" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -7592,6 +8930,15 @@
       <c r="N149" t="b">
         <v>0</v>
       </c>
+      <c r="O149" t="b">
+        <v>0</v>
+      </c>
+      <c r="P149" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q149" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -7638,6 +8985,15 @@
       <c r="N150" t="b">
         <v>0</v>
       </c>
+      <c r="O150" t="b">
+        <v>0</v>
+      </c>
+      <c r="P150" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q150" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -7684,6 +9040,15 @@
       <c r="N151" t="b">
         <v>0</v>
       </c>
+      <c r="O151" t="b">
+        <v>0</v>
+      </c>
+      <c r="P151" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q151" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -7730,6 +9095,15 @@
       <c r="N152" t="b">
         <v>0</v>
       </c>
+      <c r="O152" t="b">
+        <v>0</v>
+      </c>
+      <c r="P152" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q152" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -7776,6 +9150,15 @@
       <c r="N153" t="b">
         <v>0</v>
       </c>
+      <c r="O153" t="b">
+        <v>0</v>
+      </c>
+      <c r="P153" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q153" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -7822,6 +9205,15 @@
       <c r="N154" t="b">
         <v>0</v>
       </c>
+      <c r="O154" t="b">
+        <v>0</v>
+      </c>
+      <c r="P154" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q154" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -7868,6 +9260,15 @@
       <c r="N155" t="b">
         <v>0</v>
       </c>
+      <c r="O155" t="b">
+        <v>0</v>
+      </c>
+      <c r="P155" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q155" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -7914,6 +9315,15 @@
       <c r="N156" t="b">
         <v>0</v>
       </c>
+      <c r="O156" t="b">
+        <v>0</v>
+      </c>
+      <c r="P156" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q156" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -7960,6 +9370,15 @@
       <c r="N157" t="b">
         <v>0</v>
       </c>
+      <c r="O157" t="b">
+        <v>0</v>
+      </c>
+      <c r="P157" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q157" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -8006,6 +9425,15 @@
       <c r="N158" t="b">
         <v>0</v>
       </c>
+      <c r="O158" t="b">
+        <v>0</v>
+      </c>
+      <c r="P158" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q158" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -8052,6 +9480,15 @@
       <c r="N159" t="b">
         <v>0</v>
       </c>
+      <c r="O159" t="b">
+        <v>0</v>
+      </c>
+      <c r="P159" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q159" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -8098,6 +9535,15 @@
       <c r="N160" t="b">
         <v>0</v>
       </c>
+      <c r="O160" t="b">
+        <v>0</v>
+      </c>
+      <c r="P160" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q160" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -8144,6 +9590,15 @@
       <c r="N161" t="b">
         <v>0</v>
       </c>
+      <c r="O161" t="b">
+        <v>0</v>
+      </c>
+      <c r="P161" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q161" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -8190,6 +9645,15 @@
       <c r="N162" t="b">
         <v>0</v>
       </c>
+      <c r="O162" t="b">
+        <v>0</v>
+      </c>
+      <c r="P162" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q162" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -8236,6 +9700,15 @@
       <c r="N163" t="b">
         <v>0</v>
       </c>
+      <c r="O163" t="b">
+        <v>0</v>
+      </c>
+      <c r="P163" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q163" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -8282,6 +9755,15 @@
       <c r="N164" t="b">
         <v>0</v>
       </c>
+      <c r="O164" t="b">
+        <v>0</v>
+      </c>
+      <c r="P164" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q164" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -8328,6 +9810,15 @@
       <c r="N165" t="b">
         <v>0</v>
       </c>
+      <c r="O165" t="b">
+        <v>0</v>
+      </c>
+      <c r="P165" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q165" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -8374,6 +9865,15 @@
       <c r="N166" t="b">
         <v>0</v>
       </c>
+      <c r="O166" t="b">
+        <v>0</v>
+      </c>
+      <c r="P166" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q166" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -8420,6 +9920,15 @@
       <c r="N167" t="b">
         <v>0</v>
       </c>
+      <c r="O167" t="b">
+        <v>0</v>
+      </c>
+      <c r="P167" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q167" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -8466,6 +9975,15 @@
       <c r="N168" t="b">
         <v>0</v>
       </c>
+      <c r="O168" t="b">
+        <v>0</v>
+      </c>
+      <c r="P168" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q168" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -8512,6 +10030,15 @@
       <c r="N169" t="b">
         <v>0</v>
       </c>
+      <c r="O169" t="b">
+        <v>0</v>
+      </c>
+      <c r="P169" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q169" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -8558,6 +10085,15 @@
       <c r="N170" t="b">
         <v>0</v>
       </c>
+      <c r="O170" t="b">
+        <v>0</v>
+      </c>
+      <c r="P170" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q170" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -8604,6 +10140,15 @@
       <c r="N171" t="b">
         <v>0</v>
       </c>
+      <c r="O171" t="b">
+        <v>0</v>
+      </c>
+      <c r="P171" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q171" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -8650,6 +10195,15 @@
       <c r="N172" t="b">
         <v>0</v>
       </c>
+      <c r="O172" t="b">
+        <v>0</v>
+      </c>
+      <c r="P172" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q172" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -8696,6 +10250,15 @@
       <c r="N173" t="b">
         <v>0</v>
       </c>
+      <c r="O173" t="b">
+        <v>0</v>
+      </c>
+      <c r="P173" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q173" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -8742,6 +10305,15 @@
       <c r="N174" t="b">
         <v>0</v>
       </c>
+      <c r="O174" t="b">
+        <v>0</v>
+      </c>
+      <c r="P174" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q174" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -8788,6 +10360,15 @@
       <c r="N175" t="b">
         <v>0</v>
       </c>
+      <c r="O175" t="b">
+        <v>0</v>
+      </c>
+      <c r="P175" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q175" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -8834,6 +10415,15 @@
       <c r="N176" t="b">
         <v>0</v>
       </c>
+      <c r="O176" t="b">
+        <v>0</v>
+      </c>
+      <c r="P176" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q176" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -8880,6 +10470,15 @@
       <c r="N177" t="b">
         <v>0</v>
       </c>
+      <c r="O177" t="b">
+        <v>0</v>
+      </c>
+      <c r="P177" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q177" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -8926,6 +10525,15 @@
       <c r="N178" t="b">
         <v>0</v>
       </c>
+      <c r="O178" t="b">
+        <v>0</v>
+      </c>
+      <c r="P178" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q178" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -8972,6 +10580,15 @@
       <c r="N179" t="b">
         <v>0</v>
       </c>
+      <c r="O179" t="b">
+        <v>0</v>
+      </c>
+      <c r="P179" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q179" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -9018,6 +10635,15 @@
       <c r="N180" t="b">
         <v>0</v>
       </c>
+      <c r="O180" t="b">
+        <v>0</v>
+      </c>
+      <c r="P180" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q180" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -9064,6 +10690,15 @@
       <c r="N181" t="b">
         <v>0</v>
       </c>
+      <c r="O181" t="b">
+        <v>0</v>
+      </c>
+      <c r="P181" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q181" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -9110,6 +10745,15 @@
       <c r="N182" t="b">
         <v>0</v>
       </c>
+      <c r="O182" t="b">
+        <v>0</v>
+      </c>
+      <c r="P182" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q182" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -9156,6 +10800,15 @@
       <c r="N183" t="b">
         <v>0</v>
       </c>
+      <c r="O183" t="b">
+        <v>0</v>
+      </c>
+      <c r="P183" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q183" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -9202,6 +10855,15 @@
       <c r="N184" t="b">
         <v>0</v>
       </c>
+      <c r="O184" t="b">
+        <v>0</v>
+      </c>
+      <c r="P184" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q184" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -9248,6 +10910,15 @@
       <c r="N185" t="b">
         <v>0</v>
       </c>
+      <c r="O185" t="b">
+        <v>0</v>
+      </c>
+      <c r="P185" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q185" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -9294,6 +10965,15 @@
       <c r="N186" t="b">
         <v>0</v>
       </c>
+      <c r="O186" t="b">
+        <v>0</v>
+      </c>
+      <c r="P186" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q186" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -9340,6 +11020,15 @@
       <c r="N187" t="b">
         <v>0</v>
       </c>
+      <c r="O187" t="b">
+        <v>0</v>
+      </c>
+      <c r="P187" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q187" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -9386,6 +11075,15 @@
       <c r="N188" t="b">
         <v>0</v>
       </c>
+      <c r="O188" t="b">
+        <v>0</v>
+      </c>
+      <c r="P188" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q188" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -9432,6 +11130,15 @@
       <c r="N189" t="b">
         <v>0</v>
       </c>
+      <c r="O189" t="b">
+        <v>0</v>
+      </c>
+      <c r="P189" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q189" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -9478,6 +11185,15 @@
       <c r="N190" t="b">
         <v>0</v>
       </c>
+      <c r="O190" t="b">
+        <v>0</v>
+      </c>
+      <c r="P190" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q190" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -9524,6 +11240,15 @@
       <c r="N191" t="b">
         <v>0</v>
       </c>
+      <c r="O191" t="b">
+        <v>0</v>
+      </c>
+      <c r="P191" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q191" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -9570,6 +11295,15 @@
       <c r="N192" t="b">
         <v>0</v>
       </c>
+      <c r="O192" t="b">
+        <v>0</v>
+      </c>
+      <c r="P192" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q192" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -9616,6 +11350,15 @@
       <c r="N193" t="b">
         <v>0</v>
       </c>
+      <c r="O193" t="b">
+        <v>0</v>
+      </c>
+      <c r="P193" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q193" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -9662,6 +11405,15 @@
       <c r="N194" t="b">
         <v>0</v>
       </c>
+      <c r="O194" t="b">
+        <v>0</v>
+      </c>
+      <c r="P194" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q194" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -9708,6 +11460,15 @@
       <c r="N195" t="b">
         <v>0</v>
       </c>
+      <c r="O195" t="b">
+        <v>0</v>
+      </c>
+      <c r="P195" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q195" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -9754,6 +11515,15 @@
       <c r="N196" t="b">
         <v>0</v>
       </c>
+      <c r="O196" t="b">
+        <v>0</v>
+      </c>
+      <c r="P196" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q196" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -9800,6 +11570,15 @@
       <c r="N197" t="b">
         <v>0</v>
       </c>
+      <c r="O197" t="b">
+        <v>0</v>
+      </c>
+      <c r="P197" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q197" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -9846,6 +11625,15 @@
       <c r="N198" t="b">
         <v>0</v>
       </c>
+      <c r="O198" t="b">
+        <v>0</v>
+      </c>
+      <c r="P198" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q198" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -9892,6 +11680,15 @@
       <c r="N199" t="b">
         <v>0</v>
       </c>
+      <c r="O199" t="b">
+        <v>0</v>
+      </c>
+      <c r="P199" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q199" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -9938,6 +11735,15 @@
       <c r="N200" t="b">
         <v>0</v>
       </c>
+      <c r="O200" t="b">
+        <v>0</v>
+      </c>
+      <c r="P200" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q200" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -9984,6 +11790,15 @@
       <c r="N201" t="b">
         <v>0</v>
       </c>
+      <c r="O201" t="b">
+        <v>0</v>
+      </c>
+      <c r="P201" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q201" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -10030,6 +11845,15 @@
       <c r="N202" t="b">
         <v>0</v>
       </c>
+      <c r="O202" t="b">
+        <v>0</v>
+      </c>
+      <c r="P202" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q202" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -10076,6 +11900,15 @@
       <c r="N203" t="b">
         <v>0</v>
       </c>
+      <c r="O203" t="b">
+        <v>0</v>
+      </c>
+      <c r="P203" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q203" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -10122,6 +11955,15 @@
       <c r="N204" t="b">
         <v>0</v>
       </c>
+      <c r="O204" t="b">
+        <v>0</v>
+      </c>
+      <c r="P204" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q204" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -10168,6 +12010,15 @@
       <c r="N205" t="b">
         <v>0</v>
       </c>
+      <c r="O205" t="b">
+        <v>0</v>
+      </c>
+      <c r="P205" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q205" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -10214,6 +12065,15 @@
       <c r="N206" t="b">
         <v>0</v>
       </c>
+      <c r="O206" t="b">
+        <v>0</v>
+      </c>
+      <c r="P206" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q206" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -10260,6 +12120,15 @@
       <c r="N207" t="b">
         <v>1</v>
       </c>
+      <c r="O207" t="b">
+        <v>0</v>
+      </c>
+      <c r="P207" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q207" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -10306,6 +12175,15 @@
       <c r="N208" t="b">
         <v>1</v>
       </c>
+      <c r="O208" t="b">
+        <v>0</v>
+      </c>
+      <c r="P208" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q208" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -10352,6 +12230,15 @@
       <c r="N209" t="b">
         <v>1</v>
       </c>
+      <c r="O209" t="b">
+        <v>0</v>
+      </c>
+      <c r="P209" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q209" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -10398,6 +12285,15 @@
       <c r="N210" t="b">
         <v>1</v>
       </c>
+      <c r="O210" t="b">
+        <v>0</v>
+      </c>
+      <c r="P210" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q210" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -10444,6 +12340,15 @@
       <c r="N211" t="b">
         <v>1</v>
       </c>
+      <c r="O211" t="b">
+        <v>0</v>
+      </c>
+      <c r="P211" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q211" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -10490,6 +12395,15 @@
       <c r="N212" t="b">
         <v>0</v>
       </c>
+      <c r="O212" t="b">
+        <v>0</v>
+      </c>
+      <c r="P212" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q212" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -10536,6 +12450,15 @@
       <c r="N213" t="b">
         <v>0</v>
       </c>
+      <c r="O213" t="b">
+        <v>0</v>
+      </c>
+      <c r="P213" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q213" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -10582,6 +12505,15 @@
       <c r="N214" t="b">
         <v>0</v>
       </c>
+      <c r="O214" t="b">
+        <v>0</v>
+      </c>
+      <c r="P214" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q214" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -10628,6 +12560,15 @@
       <c r="N215" t="b">
         <v>0</v>
       </c>
+      <c r="O215" t="b">
+        <v>0</v>
+      </c>
+      <c r="P215" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q215" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -10674,6 +12615,15 @@
       <c r="N216" t="b">
         <v>0</v>
       </c>
+      <c r="O216" t="b">
+        <v>0</v>
+      </c>
+      <c r="P216" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q216" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -10720,6 +12670,15 @@
       <c r="N217" t="b">
         <v>0</v>
       </c>
+      <c r="O217" t="b">
+        <v>0</v>
+      </c>
+      <c r="P217" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q217" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -10766,6 +12725,15 @@
       <c r="N218" t="b">
         <v>0</v>
       </c>
+      <c r="O218" t="b">
+        <v>0</v>
+      </c>
+      <c r="P218" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q218" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -10812,6 +12780,15 @@
       <c r="N219" t="b">
         <v>0</v>
       </c>
+      <c r="O219" t="b">
+        <v>0</v>
+      </c>
+      <c r="P219" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q219" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -10858,6 +12835,15 @@
       <c r="N220" t="b">
         <v>0</v>
       </c>
+      <c r="O220" t="b">
+        <v>0</v>
+      </c>
+      <c r="P220" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q220" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -10904,6 +12890,15 @@
       <c r="N221" t="b">
         <v>0</v>
       </c>
+      <c r="O221" t="b">
+        <v>0</v>
+      </c>
+      <c r="P221" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q221" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -10950,6 +12945,15 @@
       <c r="N222" t="b">
         <v>0</v>
       </c>
+      <c r="O222" t="b">
+        <v>0</v>
+      </c>
+      <c r="P222" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q222" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -10996,6 +13000,15 @@
       <c r="N223" t="b">
         <v>0</v>
       </c>
+      <c r="O223" t="b">
+        <v>0</v>
+      </c>
+      <c r="P223" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q223" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -11042,6 +13055,15 @@
       <c r="N224" t="b">
         <v>0</v>
       </c>
+      <c r="O224" t="b">
+        <v>0</v>
+      </c>
+      <c r="P224" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q224" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -11088,6 +13110,15 @@
       <c r="N225" t="b">
         <v>0</v>
       </c>
+      <c r="O225" t="b">
+        <v>0</v>
+      </c>
+      <c r="P225" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q225" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -11134,6 +13165,15 @@
       <c r="N226" t="b">
         <v>0</v>
       </c>
+      <c r="O226" t="b">
+        <v>0</v>
+      </c>
+      <c r="P226" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q226" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -11180,6 +13220,15 @@
       <c r="N227" t="b">
         <v>0</v>
       </c>
+      <c r="O227" t="b">
+        <v>0</v>
+      </c>
+      <c r="P227" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q227" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -11226,6 +13275,15 @@
       <c r="N228" t="b">
         <v>0</v>
       </c>
+      <c r="O228" t="b">
+        <v>0</v>
+      </c>
+      <c r="P228" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q228" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -11272,6 +13330,15 @@
       <c r="N229" t="b">
         <v>0</v>
       </c>
+      <c r="O229" t="b">
+        <v>0</v>
+      </c>
+      <c r="P229" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q229" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -11318,6 +13385,15 @@
       <c r="N230" t="b">
         <v>0</v>
       </c>
+      <c r="O230" t="b">
+        <v>0</v>
+      </c>
+      <c r="P230" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q230" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -11364,6 +13440,15 @@
       <c r="N231" t="b">
         <v>0</v>
       </c>
+      <c r="O231" t="b">
+        <v>0</v>
+      </c>
+      <c r="P231" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q231" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -11410,6 +13495,15 @@
       <c r="N232" t="b">
         <v>0</v>
       </c>
+      <c r="O232" t="b">
+        <v>0</v>
+      </c>
+      <c r="P232" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q232" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -11456,6 +13550,15 @@
       <c r="N233" t="b">
         <v>0</v>
       </c>
+      <c r="O233" t="b">
+        <v>0</v>
+      </c>
+      <c r="P233" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q233" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -11502,6 +13605,15 @@
       <c r="N234" t="b">
         <v>0</v>
       </c>
+      <c r="O234" t="b">
+        <v>0</v>
+      </c>
+      <c r="P234" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q234" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -11548,6 +13660,15 @@
       <c r="N235" t="b">
         <v>0</v>
       </c>
+      <c r="O235" t="b">
+        <v>0</v>
+      </c>
+      <c r="P235" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q235" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -11594,6 +13715,15 @@
       <c r="N236" t="b">
         <v>0</v>
       </c>
+      <c r="O236" t="b">
+        <v>0</v>
+      </c>
+      <c r="P236" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q236" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -11640,6 +13770,15 @@
       <c r="N237" t="b">
         <v>0</v>
       </c>
+      <c r="O237" t="b">
+        <v>0</v>
+      </c>
+      <c r="P237" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q237" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -11686,6 +13825,15 @@
       <c r="N238" t="b">
         <v>0</v>
       </c>
+      <c r="O238" t="b">
+        <v>0</v>
+      </c>
+      <c r="P238" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q238" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -11732,6 +13880,15 @@
       <c r="N239" t="b">
         <v>0</v>
       </c>
+      <c r="O239" t="b">
+        <v>0</v>
+      </c>
+      <c r="P239" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q239" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -11778,6 +13935,15 @@
       <c r="N240" t="b">
         <v>0</v>
       </c>
+      <c r="O240" t="b">
+        <v>0</v>
+      </c>
+      <c r="P240" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q240" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -11824,6 +13990,15 @@
       <c r="N241" t="b">
         <v>0</v>
       </c>
+      <c r="O241" t="b">
+        <v>0</v>
+      </c>
+      <c r="P241" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q241" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -11870,6 +14045,15 @@
       <c r="N242" t="b">
         <v>0</v>
       </c>
+      <c r="O242" t="b">
+        <v>0</v>
+      </c>
+      <c r="P242" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q242" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -11916,6 +14100,15 @@
       <c r="N243" t="b">
         <v>0</v>
       </c>
+      <c r="O243" t="b">
+        <v>0</v>
+      </c>
+      <c r="P243" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q243" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -11962,6 +14155,15 @@
       <c r="N244" t="b">
         <v>0</v>
       </c>
+      <c r="O244" t="b">
+        <v>0</v>
+      </c>
+      <c r="P244" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q244" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -12008,6 +14210,15 @@
       <c r="N245" t="b">
         <v>0</v>
       </c>
+      <c r="O245" t="b">
+        <v>0</v>
+      </c>
+      <c r="P245" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q245" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -12054,6 +14265,15 @@
       <c r="N246" t="b">
         <v>0</v>
       </c>
+      <c r="O246" t="b">
+        <v>0</v>
+      </c>
+      <c r="P246" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q246" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -12100,6 +14320,15 @@
       <c r="N247" t="b">
         <v>0</v>
       </c>
+      <c r="O247" t="b">
+        <v>0</v>
+      </c>
+      <c r="P247" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q247" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -12146,6 +14375,15 @@
       <c r="N248" t="b">
         <v>0</v>
       </c>
+      <c r="O248" t="b">
+        <v>0</v>
+      </c>
+      <c r="P248" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q248" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -12192,6 +14430,15 @@
       <c r="N249" t="b">
         <v>0</v>
       </c>
+      <c r="O249" t="b">
+        <v>0</v>
+      </c>
+      <c r="P249" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q249" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -12238,6 +14485,15 @@
       <c r="N250" t="b">
         <v>0</v>
       </c>
+      <c r="O250" t="b">
+        <v>0</v>
+      </c>
+      <c r="P250" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q250" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -12284,6 +14540,15 @@
       <c r="N251" t="b">
         <v>0</v>
       </c>
+      <c r="O251" t="b">
+        <v>0</v>
+      </c>
+      <c r="P251" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q251" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -12330,6 +14595,15 @@
       <c r="N252" t="b">
         <v>0</v>
       </c>
+      <c r="O252" t="b">
+        <v>0</v>
+      </c>
+      <c r="P252" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q252" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -12376,6 +14650,15 @@
       <c r="N253" t="b">
         <v>0</v>
       </c>
+      <c r="O253" t="b">
+        <v>0</v>
+      </c>
+      <c r="P253" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q253" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -12422,6 +14705,15 @@
       <c r="N254" t="b">
         <v>0</v>
       </c>
+      <c r="O254" t="b">
+        <v>0</v>
+      </c>
+      <c r="P254" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q254" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -12468,6 +14760,15 @@
       <c r="N255" t="b">
         <v>0</v>
       </c>
+      <c r="O255" t="b">
+        <v>0</v>
+      </c>
+      <c r="P255" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q255" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -12514,6 +14815,15 @@
       <c r="N256" t="b">
         <v>0</v>
       </c>
+      <c r="O256" t="b">
+        <v>0</v>
+      </c>
+      <c r="P256" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q256" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -12560,6 +14870,15 @@
       <c r="N257" t="b">
         <v>0</v>
       </c>
+      <c r="O257" t="b">
+        <v>0</v>
+      </c>
+      <c r="P257" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q257" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -12606,6 +14925,15 @@
       <c r="N258" t="b">
         <v>0</v>
       </c>
+      <c r="O258" t="b">
+        <v>0</v>
+      </c>
+      <c r="P258" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q258" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -12652,6 +14980,15 @@
       <c r="N259" t="b">
         <v>0</v>
       </c>
+      <c r="O259" t="b">
+        <v>0</v>
+      </c>
+      <c r="P259" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q259" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -12694,7 +15031,16 @@
         <v>0</v>
       </c>
       <c r="N260" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="O260" t="b">
+        <v>1</v>
+      </c>
+      <c r="P260" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q260" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="261">
@@ -12738,7 +15084,16 @@
         <v>0</v>
       </c>
       <c r="N261" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="O261" t="b">
+        <v>1</v>
+      </c>
+      <c r="P261" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q261" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="262">
@@ -12782,7 +15137,16 @@
         <v>0</v>
       </c>
       <c r="N262" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="O262" t="b">
+        <v>1</v>
+      </c>
+      <c r="P262" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q262" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="263">
@@ -12826,7 +15190,16 @@
         <v>0</v>
       </c>
       <c r="N263" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="O263" t="b">
+        <v>1</v>
+      </c>
+      <c r="P263" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q263" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="264">
@@ -12870,7 +15243,16 @@
         <v>0</v>
       </c>
       <c r="N264" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="O264" t="b">
+        <v>1</v>
+      </c>
+      <c r="P264" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q264" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="265">
@@ -12914,7 +15296,16 @@
         <v>0</v>
       </c>
       <c r="N265" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="O265" t="b">
+        <v>1</v>
+      </c>
+      <c r="P265" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q265" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="266">
@@ -12962,6 +15353,15 @@
       <c r="N266" t="b">
         <v>0</v>
       </c>
+      <c r="O266" t="b">
+        <v>0</v>
+      </c>
+      <c r="P266" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q266" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -13008,6 +15408,15 @@
       <c r="N267" t="b">
         <v>0</v>
       </c>
+      <c r="O267" t="b">
+        <v>0</v>
+      </c>
+      <c r="P267" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q267" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -13054,6 +15463,15 @@
       <c r="N268" t="b">
         <v>0</v>
       </c>
+      <c r="O268" t="b">
+        <v>0</v>
+      </c>
+      <c r="P268" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q268" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -13100,6 +15518,15 @@
       <c r="N269" t="b">
         <v>0</v>
       </c>
+      <c r="O269" t="b">
+        <v>0</v>
+      </c>
+      <c r="P269" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q269" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -13146,6 +15573,15 @@
       <c r="N270" t="b">
         <v>0</v>
       </c>
+      <c r="O270" t="b">
+        <v>0</v>
+      </c>
+      <c r="P270" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q270" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -13192,6 +15628,15 @@
       <c r="N271" t="b">
         <v>0</v>
       </c>
+      <c r="O271" t="b">
+        <v>0</v>
+      </c>
+      <c r="P271" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q271" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -13238,6 +15683,15 @@
       <c r="N272" t="b">
         <v>0</v>
       </c>
+      <c r="O272" t="b">
+        <v>0</v>
+      </c>
+      <c r="P272" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q272" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -13284,6 +15738,15 @@
       <c r="N273" t="b">
         <v>0</v>
       </c>
+      <c r="O273" t="b">
+        <v>0</v>
+      </c>
+      <c r="P273" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q273" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -13330,6 +15793,15 @@
       <c r="N274" t="b">
         <v>0</v>
       </c>
+      <c r="O274" t="b">
+        <v>0</v>
+      </c>
+      <c r="P274" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q274" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -13376,6 +15848,15 @@
       <c r="N275" t="b">
         <v>0</v>
       </c>
+      <c r="O275" t="b">
+        <v>0</v>
+      </c>
+      <c r="P275" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q275" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -13420,7 +15901,16 @@
         <v>0</v>
       </c>
       <c r="N276" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="O276" t="b">
+        <v>1</v>
+      </c>
+      <c r="P276" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q276" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="277">
@@ -13466,7 +15956,16 @@
         <v>0</v>
       </c>
       <c r="N277" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="O277" t="b">
+        <v>1</v>
+      </c>
+      <c r="P277" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q277" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="278">
@@ -13512,7 +16011,16 @@
         <v>0</v>
       </c>
       <c r="N278" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="O278" t="b">
+        <v>1</v>
+      </c>
+      <c r="P278" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q278" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="279">
@@ -13558,7 +16066,16 @@
         <v>0</v>
       </c>
       <c r="N279" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="O279" t="b">
+        <v>1</v>
+      </c>
+      <c r="P279" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q279" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="280">
@@ -13604,7 +16121,16 @@
         <v>0</v>
       </c>
       <c r="N280" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="O280" t="b">
+        <v>1</v>
+      </c>
+      <c r="P280" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q280" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="281">
@@ -13650,7 +16176,16 @@
         <v>0</v>
       </c>
       <c r="N281" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="O281" t="b">
+        <v>1</v>
+      </c>
+      <c r="P281" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q281" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="282">
@@ -13698,6 +16233,15 @@
       <c r="N282" t="b">
         <v>0</v>
       </c>
+      <c r="O282" t="b">
+        <v>0</v>
+      </c>
+      <c r="P282" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q282" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -13744,6 +16288,15 @@
       <c r="N283" t="b">
         <v>0</v>
       </c>
+      <c r="O283" t="b">
+        <v>0</v>
+      </c>
+      <c r="P283" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q283" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -13790,6 +16343,15 @@
       <c r="N284" t="b">
         <v>0</v>
       </c>
+      <c r="O284" t="b">
+        <v>0</v>
+      </c>
+      <c r="P284" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q284" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -13834,6 +16396,15 @@
         <v>0</v>
       </c>
       <c r="N285" t="b">
+        <v>0</v>
+      </c>
+      <c r="O285" t="b">
+        <v>0</v>
+      </c>
+      <c r="P285" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q285" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13919,16 +16490,16 @@
         <v>0.01198061318956598</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3847410553831073</v>
+        <v>0.01198452906248298</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3104067962751185</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0.9312203888253554</v>
       </c>
       <c r="I2" t="n">
-        <v>4.978304803741824</v>
+        <v>4.998671412055952</v>
       </c>
     </row>
     <row r="3">
@@ -13952,16 +16523,16 @@
         <v>0.2543157436148777</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6246256058378261</v>
+        <v>0.2543988669172523</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6208135925502369</v>
+        <v>0.3104067962751185</v>
       </c>
       <c r="H3" t="n">
         <v>1.241627185100474</v>
       </c>
       <c r="I3" t="n">
-        <v>4.966942886359648</v>
+        <v>4.987280813253194</v>
       </c>
     </row>
   </sheetData>
